--- a/data/source/weekly/cs-en-us-018pct.xlsx
+++ b/data/source/weekly/cs-en-us-018pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -895,20 +895,20 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="15">
-        <v>2</v>
-      </c>
-      <c r="E15" s="14">
-        <v>-100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="15">
         <v>1</v>
       </c>
       <c r="G15" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H15" s="14">
-        <v>-75</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I15" s="15">
         <v>1</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D16" s="15">
         <v>3</v>
       </c>
       <c r="E16" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F16" s="15">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G16" s="15">
+        <v>17</v>
+      </c>
+      <c r="H16" s="14">
+        <v>-23.529411764705</v>
+      </c>
+      <c r="I16" s="15">
         <v>18</v>
       </c>
-      <c r="H16" s="14">
-        <v>-38.888888888888</v>
-      </c>
-      <c r="I16" s="15">
-        <v>15</v>
-      </c>
       <c r="J16" s="15">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K16" s="14">
-        <v>-40</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="L16" s="14">
-        <v>-37.5</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="M16" s="14">
-        <v>-6.25</v>
+        <v>12.5</v>
       </c>
       <c r="N16" s="14">
-        <v>-87.5</v>
+        <v>-87.919463087248</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D17" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E17" s="14">
-        <v>80</v>
+        <v>-50</v>
       </c>
       <c r="F17" s="15">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G17" s="15">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H17" s="14">
         <v>0</v>
       </c>
       <c r="I17" s="15">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="J17" s="15">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="K17" s="14">
-        <v>3.333333333333</v>
+        <v>-5.555555555555</v>
       </c>
       <c r="L17" s="14">
-        <v>82.352941176470</v>
+        <v>88.888888888888</v>
       </c>
       <c r="M17" s="14">
-        <v>93.75</v>
+        <v>112.5</v>
       </c>
       <c r="N17" s="14">
-        <v>-36.734693877551</v>
+        <v>-37.037037037037</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1018,38 +1018,38 @@
       <c r="C18" s="15">
         <v>3</v>
       </c>
-      <c r="D18" s="15">
-        <v>4</v>
-      </c>
-      <c r="E18" s="14">
-        <v>-25</v>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F18" s="15">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G18" s="15">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H18" s="14">
-        <v>-27.777777777777</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="I18" s="15">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J18" s="15">
         <v>23</v>
       </c>
       <c r="K18" s="14">
-        <v>-30.434782608695</v>
+        <v>-17.391304347826</v>
       </c>
       <c r="L18" s="14">
-        <v>-20</v>
+        <v>-24</v>
       </c>
       <c r="M18" s="14">
-        <v>-33.333333333333</v>
+        <v>-34.482758620689</v>
       </c>
       <c r="N18" s="14">
-        <v>-93.415637860082</v>
+        <v>-93.379790940766</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="D19" s="15">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E19" s="14">
-        <v>-16.129032258064</v>
+        <v>6.25</v>
       </c>
       <c r="F19" s="15">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G19" s="15">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="H19" s="14">
-        <v>2.419354838709</v>
+        <v>5.982905982905</v>
       </c>
       <c r="I19" s="15">
-        <v>181</v>
+        <v>215</v>
       </c>
       <c r="J19" s="15">
-        <v>186</v>
+        <v>218</v>
       </c>
       <c r="K19" s="14">
-        <v>-2.688172043010</v>
+        <v>-1.376146788990</v>
       </c>
       <c r="L19" s="14">
-        <v>-12.135922330097</v>
+        <v>-10.041841004184</v>
       </c>
       <c r="M19" s="14">
-        <v>4.624277456647</v>
+        <v>10.256410256410</v>
       </c>
       <c r="N19" s="14">
-        <v>-75.672043010752</v>
+        <v>-75.344036697247</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,37 +1101,37 @@
         <v>20</v>
       </c>
       <c r="D20" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E20" s="14">
         <v>-100</v>
       </c>
       <c r="F20" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G20" s="15">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H20" s="14">
-        <v>33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="I20" s="15">
         <v>4</v>
       </c>
       <c r="J20" s="15">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K20" s="14">
-        <v>0</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="L20" s="14">
         <v>-33.333333333333</v>
       </c>
       <c r="M20" s="14">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="N20" s="14">
-        <v>-92.156862745098</v>
+        <v>-93.103448275862</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
+        <v>43</v>
+      </c>
+      <c r="D21" s="17">
         <v>44</v>
       </c>
-      <c r="D21" s="17">
-        <v>46</v>
-      </c>
       <c r="E21" s="18">
-        <v>-4.347826086956</v>
+        <v>-2.272727272727</v>
       </c>
       <c r="F21" s="17">
+        <v>172</v>
+      </c>
+      <c r="G21" s="17">
         <v>175</v>
       </c>
-      <c r="G21" s="17">
-        <v>186</v>
-      </c>
       <c r="H21" s="18">
-        <v>-5.913978494623</v>
+        <v>-1.714285714285</v>
       </c>
       <c r="I21" s="17">
-        <v>248</v>
+        <v>291</v>
       </c>
       <c r="J21" s="17">
-        <v>274</v>
+        <v>318</v>
       </c>
       <c r="K21" s="18">
-        <v>-9.489051094890</v>
+        <v>-8.490566037735</v>
       </c>
       <c r="L21" s="18">
-        <v>-9.818181818181</v>
+        <v>-7.911392405063</v>
       </c>
       <c r="M21" s="18">
-        <v>2.904564315352</v>
+        <v>8.178438661710</v>
       </c>
       <c r="N21" s="18">
-        <v>-79.655455291222</v>
+        <v>-79.678770949720</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1183,31 +1183,31 @@
         <v>1</v>
       </c>
       <c r="D22" s="15">
+        <v>2</v>
+      </c>
+      <c r="E22" s="14">
+        <v>-50</v>
+      </c>
+      <c r="F22" s="15">
         <v>4</v>
       </c>
-      <c r="E22" s="14">
-        <v>-75</v>
-      </c>
-      <c r="F22" s="15">
-        <v>6</v>
-      </c>
       <c r="G22" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H22" s="14">
-        <v>0</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="I22" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J22" s="15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K22" s="14">
-        <v>-25</v>
+        <v>-30</v>
       </c>
       <c r="L22" s="14">
-        <v>-25</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="M22" s="14">
         <v>0</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="D24" s="15">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="E24" s="14">
-        <v>-15.217391304347</v>
+        <v>51.351351351351</v>
       </c>
       <c r="F24" s="15">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G24" s="15">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="H24" s="14">
-        <v>-14.851485148514</v>
+        <v>-8.947368421052</v>
       </c>
       <c r="I24" s="15">
-        <v>246</v>
+        <v>301</v>
       </c>
       <c r="J24" s="15">
-        <v>270</v>
+        <v>307</v>
       </c>
       <c r="K24" s="14">
-        <v>-8.888888888888</v>
+        <v>-1.954397394136</v>
       </c>
       <c r="L24" s="14">
-        <v>-19.869706840390</v>
+        <v>-15.211267605633</v>
       </c>
       <c r="M24" s="14">
-        <v>31.550802139037</v>
+        <v>48.275862068965</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="D25" s="15">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="E25" s="14">
-        <v>-26.923076923076</v>
+        <v>11.363636363636</v>
       </c>
       <c r="F25" s="15">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="G25" s="15">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="H25" s="14">
-        <v>-26.415094339622</v>
+        <v>-26.086956521739</v>
       </c>
       <c r="I25" s="15">
-        <v>232</v>
+        <v>281</v>
       </c>
       <c r="J25" s="15">
-        <v>279</v>
+        <v>323</v>
       </c>
       <c r="K25" s="14">
-        <v>-16.845878136200</v>
+        <v>-13.003095975232</v>
       </c>
       <c r="L25" s="14">
-        <v>-23.432343234323</v>
+        <v>-20.621468926553</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D26" s="15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E26" s="14">
-        <v>-50</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="F26" s="15">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="G26" s="15">
         <v>42</v>
       </c>
       <c r="H26" s="14">
-        <v>4.761904761904</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I26" s="15">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="J26" s="15">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="K26" s="14">
-        <v>15.789473684210</v>
+        <v>4.285714285714</v>
       </c>
       <c r="L26" s="14">
-        <v>1.538461538461</v>
+        <v>-13.095238095238</v>
       </c>
       <c r="M26" s="14">
-        <v>29.411764705882</v>
+        <v>19.672131147541</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,20 +1387,20 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="15">
-        <v>2</v>
-      </c>
-      <c r="E27" s="14">
-        <v>-100</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="15">
         <v>1</v>
       </c>
       <c r="G27" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H27" s="14">
-        <v>-75</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I27" s="15">
         <v>1</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D28" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E28" s="14">
-        <v>-75</v>
+        <v>-40</v>
       </c>
       <c r="F28" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G28" s="15">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H28" s="14">
-        <v>-33.333333333333</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="I28" s="15">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J28" s="15">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="K28" s="14">
-        <v>-16.666666666666</v>
+        <v>-23.529411764705</v>
       </c>
       <c r="L28" s="14">
-        <v>233.333333333333</v>
+        <v>225</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1560,11 +1560,11 @@
       <c r="F31" s="15">
         <v>2</v>
       </c>
-      <c r="G31" s="15">
-        <v>1</v>
-      </c>
-      <c r="H31" s="14">
-        <v>100</v>
+      <c r="G31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I31" s="15">
         <v>2</v>
@@ -1610,17 +1610,17 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>21</v>
+      <c r="D33" s="15">
+        <v>1</v>
+      </c>
+      <c r="E33" s="14">
+        <v>-100</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G33" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H33" s="14">
         <v>-100</v>
@@ -1629,7 +1629,7 @@
         <v>20</v>
       </c>
       <c r="J33" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K33" s="14">
         <v>-100</v>

--- a/data/source/weekly/cs-en-us-018pct.xlsx
+++ b/data/source/weekly/cs-en-us-018pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="15">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -905,28 +905,28 @@
         <v>1</v>
       </c>
       <c r="G15" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H15" s="14">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="I15" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J15" s="15">
         <v>6</v>
       </c>
       <c r="K15" s="14">
-        <v>-83.333333333333</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L15" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M15" s="14">
-        <v>-83.333333333333</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N15" s="14">
-        <v>-87.5</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D16" s="15">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E16" s="14">
+        <v>-71.428571428571</v>
+      </c>
+      <c r="F16" s="15">
+        <v>14</v>
+      </c>
+      <c r="G16" s="15">
+        <v>16</v>
+      </c>
+      <c r="H16" s="14">
+        <v>-12.5</v>
+      </c>
+      <c r="I16" s="15">
+        <v>20</v>
+      </c>
+      <c r="J16" s="15">
+        <v>35</v>
+      </c>
+      <c r="K16" s="14">
+        <v>-42.857142857142</v>
+      </c>
+      <c r="L16" s="14">
+        <v>-31.034482758620</v>
+      </c>
+      <c r="M16" s="14">
         <v>0</v>
       </c>
-      <c r="F16" s="15">
-        <v>13</v>
-      </c>
-      <c r="G16" s="15">
-        <v>17</v>
-      </c>
-      <c r="H16" s="14">
-        <v>-23.529411764705</v>
-      </c>
-      <c r="I16" s="15">
-        <v>18</v>
-      </c>
-      <c r="J16" s="15">
-        <v>28</v>
-      </c>
-      <c r="K16" s="14">
-        <v>-35.714285714285</v>
-      </c>
-      <c r="L16" s="14">
-        <v>-30.769230769230</v>
-      </c>
-      <c r="M16" s="14">
-        <v>12.5</v>
-      </c>
       <c r="N16" s="14">
-        <v>-87.919463087248</v>
+        <v>-88.505747126436</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D17" s="15">
         <v>6</v>
       </c>
       <c r="E17" s="14">
-        <v>-50</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F17" s="15">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G17" s="15">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H17" s="14">
+        <v>-8.333333333333</v>
+      </c>
+      <c r="I17" s="15">
+        <v>42</v>
+      </c>
+      <c r="J17" s="15">
+        <v>42</v>
+      </c>
+      <c r="K17" s="14">
         <v>0</v>
       </c>
-      <c r="I17" s="15">
-        <v>34</v>
-      </c>
-      <c r="J17" s="15">
-        <v>36</v>
-      </c>
-      <c r="K17" s="14">
-        <v>-5.555555555555</v>
-      </c>
       <c r="L17" s="14">
-        <v>88.888888888888</v>
+        <v>55.555555555555</v>
       </c>
       <c r="M17" s="14">
-        <v>112.5</v>
+        <v>147.058823529412</v>
       </c>
       <c r="N17" s="14">
-        <v>-37.037037037037</v>
+        <v>-32.258064516129</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
+        <v>4</v>
+      </c>
+      <c r="D18" s="15">
         <v>3</v>
       </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
+      <c r="E18" s="14">
+        <v>33.333333333333</v>
       </c>
       <c r="F18" s="15">
+        <v>13</v>
+      </c>
+      <c r="G18" s="15">
         <v>11</v>
       </c>
-      <c r="G18" s="15">
-        <v>12</v>
-      </c>
       <c r="H18" s="14">
-        <v>-8.333333333333</v>
+        <v>18.181818181818</v>
       </c>
       <c r="I18" s="15">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J18" s="15">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K18" s="14">
-        <v>-17.391304347826</v>
+        <v>-11.538461538461</v>
       </c>
       <c r="L18" s="14">
-        <v>-24</v>
+        <v>-11.538461538461</v>
       </c>
       <c r="M18" s="14">
-        <v>-34.482758620689</v>
+        <v>-28.125</v>
       </c>
       <c r="N18" s="14">
-        <v>-93.379790940766</v>
+        <v>-93.134328358209</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D19" s="15">
         <v>32</v>
       </c>
       <c r="E19" s="14">
-        <v>6.25</v>
+        <v>12.5</v>
       </c>
       <c r="F19" s="15">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G19" s="15">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="H19" s="14">
-        <v>5.982905982905</v>
+        <v>1.680672268907</v>
       </c>
       <c r="I19" s="15">
-        <v>215</v>
+        <v>251</v>
       </c>
       <c r="J19" s="15">
-        <v>218</v>
+        <v>250</v>
       </c>
       <c r="K19" s="14">
-        <v>-1.376146788990</v>
+        <v>0.4</v>
       </c>
       <c r="L19" s="14">
-        <v>-10.041841004184</v>
+        <v>-5.639097744360</v>
       </c>
       <c r="M19" s="14">
-        <v>10.256410256410</v>
+        <v>8.658008658008</v>
       </c>
       <c r="N19" s="14">
-        <v>-75.344036697247</v>
+        <v>-75.173095944609</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,37 +1101,37 @@
         <v>20</v>
       </c>
       <c r="D20" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E20" s="14">
         <v>-100</v>
       </c>
       <c r="F20" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G20" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H20" s="14">
-        <v>-50</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="I20" s="15">
         <v>4</v>
       </c>
       <c r="J20" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K20" s="14">
-        <v>-42.857142857142</v>
+        <v>-50</v>
       </c>
       <c r="L20" s="14">
         <v>-33.333333333333</v>
       </c>
       <c r="M20" s="14">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="N20" s="14">
-        <v>-93.103448275862</v>
+        <v>-94.285714285714</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="D21" s="17">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E21" s="18">
-        <v>-2.272727272727</v>
+        <v>4.081632653061</v>
       </c>
       <c r="F21" s="17">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G21" s="17">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="H21" s="18">
-        <v>-1.714285714285</v>
+        <v>-3.351955307262</v>
       </c>
       <c r="I21" s="17">
-        <v>291</v>
+        <v>342</v>
       </c>
       <c r="J21" s="17">
-        <v>318</v>
+        <v>367</v>
       </c>
       <c r="K21" s="18">
-        <v>-8.490566037735</v>
+        <v>-6.811989100817</v>
       </c>
       <c r="L21" s="18">
-        <v>-7.911392405063</v>
+        <v>-3.932584269662</v>
       </c>
       <c r="M21" s="18">
-        <v>8.178438661710</v>
+        <v>8.917197452229</v>
       </c>
       <c r="N21" s="18">
-        <v>-79.678770949720</v>
+        <v>-79.471788715486</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>29</v>
       </c>
       <c r="C22" s="15">
-        <v>1</v>
-      </c>
-      <c r="D22" s="15">
         <v>2</v>
       </c>
-      <c r="E22" s="14">
-        <v>-50</v>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="15">
         <v>4</v>
       </c>
       <c r="G22" s="15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H22" s="14">
-        <v>-42.857142857142</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I22" s="15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J22" s="15">
         <v>10</v>
       </c>
       <c r="K22" s="14">
-        <v>-30</v>
+        <v>-10</v>
       </c>
       <c r="L22" s="14">
-        <v>-22.222222222222</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="M22" s="14">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1232,11 +1232,11 @@
       <c r="F23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G23" s="15">
-        <v>1</v>
-      </c>
-      <c r="H23" s="14">
-        <v>-100</v>
+      <c r="G23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I23" s="13" t="s">
         <v>20</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D24" s="15">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E24" s="14">
-        <v>51.351351351351</v>
+        <v>8.163265306122</v>
       </c>
       <c r="F24" s="15">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="G24" s="15">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="H24" s="14">
-        <v>-8.947368421052</v>
+        <v>-6.632653061224</v>
       </c>
       <c r="I24" s="15">
-        <v>301</v>
+        <v>354</v>
       </c>
       <c r="J24" s="15">
-        <v>307</v>
+        <v>356</v>
       </c>
       <c r="K24" s="14">
-        <v>-1.954397394136</v>
+        <v>-0.561797752808</v>
       </c>
       <c r="L24" s="14">
-        <v>-15.211267605633</v>
+        <v>-14.077669902912</v>
       </c>
       <c r="M24" s="14">
-        <v>48.275862068965</v>
+        <v>46.887966804979</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D25" s="15">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E25" s="14">
-        <v>11.363636363636</v>
+        <v>10.869565217391</v>
       </c>
       <c r="F25" s="15">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="G25" s="15">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="H25" s="14">
-        <v>-26.086956521739</v>
+        <v>-16</v>
       </c>
       <c r="I25" s="15">
-        <v>281</v>
+        <v>332</v>
       </c>
       <c r="J25" s="15">
-        <v>323</v>
+        <v>369</v>
       </c>
       <c r="K25" s="14">
-        <v>-13.003095975232</v>
+        <v>-10.027100271002</v>
       </c>
       <c r="L25" s="14">
-        <v>-20.621468926553</v>
+        <v>-19.221411192214</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D26" s="15">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E26" s="14">
-        <v>-38.461538461538</v>
+        <v>36.363636363636</v>
       </c>
       <c r="F26" s="15">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G26" s="15">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H26" s="14">
-        <v>-14.285714285714</v>
+        <v>-15.909090909090</v>
       </c>
       <c r="I26" s="15">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="J26" s="15">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="K26" s="14">
-        <v>4.285714285714</v>
+        <v>7.407407407407</v>
       </c>
       <c r="L26" s="14">
-        <v>-13.095238095238</v>
+        <v>-3.333333333333</v>
       </c>
       <c r="M26" s="14">
-        <v>19.672131147541</v>
+        <v>22.535211267605</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="15">
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1397,22 +1397,22 @@
         <v>1</v>
       </c>
       <c r="G27" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H27" s="14">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="I27" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J27" s="15">
         <v>7</v>
       </c>
       <c r="K27" s="14">
-        <v>-85.714285714285</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="L27" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1429,31 +1429,31 @@
         <v>3</v>
       </c>
       <c r="D28" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E28" s="14">
-        <v>-40</v>
+        <v>-50</v>
       </c>
       <c r="F28" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G28" s="15">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="H28" s="14">
-        <v>-41.666666666666</v>
+        <v>-52.941176470588</v>
       </c>
       <c r="I28" s="15">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J28" s="15">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="K28" s="14">
-        <v>-23.529411764705</v>
+        <v>-30.434782608695</v>
       </c>
       <c r="L28" s="14">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1610,11 +1610,11 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="15">
-        <v>1</v>
-      </c>
-      <c r="E33" s="14">
-        <v>-100</v>
+      <c r="D33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-018pct.xlsx
+++ b/data/source/weekly/cs-en-us-018pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -902,31 +902,31 @@
         <v>21</v>
       </c>
       <c r="F15" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="15">
         <v>2</v>
       </c>
       <c r="H15" s="14">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I15" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J15" s="15">
         <v>6</v>
       </c>
       <c r="K15" s="14">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="L15" s="14">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="M15" s="14">
-        <v>-66.666666666666</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="N15" s="14">
-        <v>-80</v>
+        <v>-70</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D16" s="15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E16" s="14">
-        <v>-71.428571428571</v>
+        <v>-20</v>
       </c>
       <c r="F16" s="15">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G16" s="15">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H16" s="14">
-        <v>-12.5</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I16" s="15">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J16" s="15">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="K16" s="14">
-        <v>-42.857142857142</v>
+        <v>-40</v>
       </c>
       <c r="L16" s="14">
-        <v>-31.034482758620</v>
+        <v>-35.135135135135</v>
       </c>
       <c r="M16" s="14">
-        <v>0</v>
+        <v>4.347826086956</v>
       </c>
       <c r="N16" s="14">
-        <v>-88.505747126436</v>
+        <v>-88.349514563106</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D17" s="15">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E17" s="14">
-        <v>33.333333333333</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="F17" s="15">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G17" s="15">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H17" s="14">
-        <v>-8.333333333333</v>
+        <v>-3.846153846153</v>
       </c>
       <c r="I17" s="15">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="J17" s="15">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="K17" s="14">
-        <v>0</v>
+        <v>-7.843137254901</v>
       </c>
       <c r="L17" s="14">
-        <v>55.555555555555</v>
+        <v>62.068965517241</v>
       </c>
       <c r="M17" s="14">
-        <v>147.058823529412</v>
+        <v>135</v>
       </c>
       <c r="N17" s="14">
-        <v>-32.258064516129</v>
+        <v>-31.884057971014</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,37 +1019,37 @@
         <v>4</v>
       </c>
       <c r="D18" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E18" s="14">
-        <v>33.333333333333</v>
+        <v>-20</v>
       </c>
       <c r="F18" s="15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G18" s="15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H18" s="14">
-        <v>18.181818181818</v>
+        <v>16.666666666666</v>
       </c>
       <c r="I18" s="15">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J18" s="15">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="K18" s="14">
-        <v>-11.538461538461</v>
+        <v>-12.903225806451</v>
       </c>
       <c r="L18" s="14">
-        <v>-11.538461538461</v>
+        <v>-10</v>
       </c>
       <c r="M18" s="14">
-        <v>-28.125</v>
+        <v>-28.947368421052</v>
       </c>
       <c r="N18" s="14">
-        <v>-93.134328358209</v>
+        <v>-92.582417582417</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D19" s="15">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="E19" s="14">
-        <v>12.5</v>
+        <v>-20.454545454545</v>
       </c>
       <c r="F19" s="15">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="G19" s="15">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="H19" s="14">
-        <v>1.680672268907</v>
+        <v>-5.755395683453</v>
       </c>
       <c r="I19" s="15">
-        <v>251</v>
+        <v>286</v>
       </c>
       <c r="J19" s="15">
-        <v>250</v>
+        <v>294</v>
       </c>
       <c r="K19" s="14">
-        <v>0.4</v>
+        <v>-2.721088435374</v>
       </c>
       <c r="L19" s="14">
-        <v>-5.639097744360</v>
+        <v>-1.718213058419</v>
       </c>
       <c r="M19" s="14">
-        <v>8.658008658008</v>
+        <v>12.598425196850</v>
       </c>
       <c r="N19" s="14">
-        <v>-75.173095944609</v>
+        <v>-74.734982332155</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1106,32 +1106,32 @@
       <c r="E20" s="14">
         <v>-100</v>
       </c>
-      <c r="F20" s="15">
-        <v>2</v>
+      <c r="F20" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G20" s="15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H20" s="14">
-        <v>-71.428571428571</v>
+        <v>-100</v>
       </c>
       <c r="I20" s="15">
         <v>4</v>
       </c>
       <c r="J20" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K20" s="14">
-        <v>-50</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="L20" s="14">
+        <v>-42.857142857142</v>
+      </c>
+      <c r="M20" s="14">
         <v>-33.333333333333</v>
       </c>
-      <c r="M20" s="14">
-        <v>-20</v>
-      </c>
       <c r="N20" s="14">
-        <v>-94.285714285714</v>
+        <v>-94.936708860759</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D21" s="17">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="E21" s="18">
-        <v>4.081632653061</v>
+        <v>-25</v>
       </c>
       <c r="F21" s="17">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="G21" s="17">
-        <v>179</v>
+        <v>203</v>
       </c>
       <c r="H21" s="18">
-        <v>-3.351955307262</v>
+        <v>-7.881773399014</v>
       </c>
       <c r="I21" s="17">
-        <v>342</v>
+        <v>391</v>
       </c>
       <c r="J21" s="17">
-        <v>367</v>
+        <v>431</v>
       </c>
       <c r="K21" s="18">
-        <v>-6.811989100817</v>
+        <v>-9.280742459396</v>
       </c>
       <c r="L21" s="18">
-        <v>-3.932584269662</v>
+        <v>-1.262626262626</v>
       </c>
       <c r="M21" s="18">
-        <v>8.917197452229</v>
+        <v>11.396011396011</v>
       </c>
       <c r="N21" s="18">
-        <v>-79.471788715486</v>
+        <v>-79.023605150214</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,35 +1182,35 @@
       <c r="C22" s="15">
         <v>2</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="D22" s="15">
+        <v>3</v>
+      </c>
+      <c r="E22" s="14">
+        <v>-33.333333333333</v>
       </c>
       <c r="F22" s="15">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G22" s="15">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H22" s="14">
-        <v>-33.333333333333</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="I22" s="15">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J22" s="15">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K22" s="14">
-        <v>-10</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="L22" s="14">
-        <v>-18.181818181818</v>
+        <v>0</v>
       </c>
       <c r="M22" s="14">
-        <v>12.5</v>
+        <v>33.333333333333</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="D24" s="15">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="E24" s="14">
-        <v>8.163265306122</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="F24" s="15">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="G24" s="15">
-        <v>196</v>
+        <v>176</v>
       </c>
       <c r="H24" s="14">
-        <v>-6.632653061224</v>
+        <v>1.704545454545</v>
       </c>
       <c r="I24" s="15">
-        <v>354</v>
+        <v>386</v>
       </c>
       <c r="J24" s="15">
-        <v>356</v>
+        <v>400</v>
       </c>
       <c r="K24" s="14">
-        <v>-0.561797752808</v>
+        <v>-3.5</v>
       </c>
       <c r="L24" s="14">
-        <v>-14.077669902912</v>
+        <v>-19.750519750519</v>
       </c>
       <c r="M24" s="14">
-        <v>46.887966804979</v>
+        <v>43.494423791821</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="D25" s="15">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E25" s="14">
-        <v>10.869565217391</v>
+        <v>-20.454545454545</v>
       </c>
       <c r="F25" s="15">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="G25" s="15">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="H25" s="14">
-        <v>-16</v>
+        <v>-6.989247311827</v>
       </c>
       <c r="I25" s="15">
-        <v>332</v>
+        <v>367</v>
       </c>
       <c r="J25" s="15">
-        <v>369</v>
+        <v>413</v>
       </c>
       <c r="K25" s="14">
-        <v>-10.027100271002</v>
+        <v>-11.138014527845</v>
       </c>
       <c r="L25" s="14">
-        <v>-19.221411192214</v>
+        <v>-22.410147991543</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D26" s="15">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E26" s="14">
-        <v>36.363636363636</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="F26" s="15">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G26" s="15">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="H26" s="14">
-        <v>-15.909090909090</v>
+        <v>-20</v>
       </c>
       <c r="I26" s="15">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="J26" s="15">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="K26" s="14">
-        <v>7.407407407407</v>
+        <v>3.157894736842</v>
       </c>
       <c r="L26" s="14">
-        <v>-3.333333333333</v>
+        <v>-3.921568627450</v>
       </c>
       <c r="M26" s="14">
-        <v>22.535211267605</v>
+        <v>28.947368421052</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1394,25 +1394,25 @@
         <v>21</v>
       </c>
       <c r="F27" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27" s="15">
         <v>2</v>
       </c>
       <c r="H27" s="14">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I27" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J27" s="15">
         <v>7</v>
       </c>
       <c r="K27" s="14">
-        <v>-71.428571428571</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="L27" s="14">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D28" s="15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E28" s="14">
-        <v>-50</v>
+        <v>-80</v>
       </c>
       <c r="F28" s="15">
         <v>8</v>
       </c>
       <c r="G28" s="15">
+        <v>20</v>
+      </c>
+      <c r="H28" s="14">
+        <v>-60</v>
+      </c>
+      <c r="I28" s="15">
         <v>17</v>
       </c>
-      <c r="H28" s="14">
-        <v>-52.941176470588</v>
-      </c>
-      <c r="I28" s="15">
-        <v>16</v>
-      </c>
       <c r="J28" s="15">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="K28" s="14">
-        <v>-30.434782608695</v>
+        <v>-39.285714285714</v>
       </c>
       <c r="L28" s="14">
-        <v>220</v>
+        <v>183.333333333333</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1558,7 +1558,7 @@
         <v>21</v>
       </c>
       <c r="F31" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1576,7 +1576,7 @@
         <v>100</v>
       </c>
       <c r="L31" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1610,11 +1610,11 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>21</v>
+      <c r="D33" s="15">
+        <v>1</v>
+      </c>
+      <c r="E33" s="14">
+        <v>-100</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
@@ -1629,7 +1629,7 @@
         <v>20</v>
       </c>
       <c r="J33" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K33" s="14">
         <v>-100</v>

--- a/data/source/weekly/cs-en-us-018pct.xlsx
+++ b/data/source/weekly/cs-en-us-018pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -895,38 +895,38 @@
       <c r="C15" s="15">
         <v>1</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="15">
+        <v>1</v>
+      </c>
+      <c r="E15" s="14">
+        <v>0</v>
       </c>
       <c r="F15" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G15" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H15" s="14">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I15" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J15" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K15" s="14">
-        <v>-50</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="L15" s="14">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="M15" s="14">
-        <v>-57.142857142857</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="N15" s="14">
-        <v>-70</v>
+        <v>-60</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -943,31 +943,31 @@
         <v>-20</v>
       </c>
       <c r="F16" s="15">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G16" s="15">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H16" s="14">
-        <v>-16.666666666666</v>
+        <v>-35</v>
       </c>
       <c r="I16" s="15">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J16" s="15">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="K16" s="14">
-        <v>-40</v>
+        <v>-37.777777777777</v>
       </c>
       <c r="L16" s="14">
-        <v>-35.135135135135</v>
+        <v>-26.315789473684</v>
       </c>
       <c r="M16" s="14">
-        <v>4.347826086956</v>
+        <v>12</v>
       </c>
       <c r="N16" s="14">
-        <v>-88.349514563106</v>
+        <v>-88.429752066115</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,78 +978,78 @@
         <v>4</v>
       </c>
       <c r="D17" s="15">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E17" s="14">
-        <v>-55.555555555555</v>
+        <v>-20</v>
       </c>
       <c r="F17" s="15">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="G17" s="15">
         <v>26</v>
       </c>
       <c r="H17" s="14">
-        <v>-3.846153846153</v>
+        <v>-26.923076923076</v>
       </c>
       <c r="I17" s="15">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="J17" s="15">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="K17" s="14">
-        <v>-7.843137254901</v>
+        <v>-8.928571428571</v>
       </c>
       <c r="L17" s="14">
-        <v>62.068965517241</v>
+        <v>50</v>
       </c>
       <c r="M17" s="14">
-        <v>135</v>
+        <v>121.739130434783</v>
       </c>
       <c r="N17" s="14">
-        <v>-31.884057971014</v>
+        <v>-32</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="15">
-        <v>4</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="15">
         <v>5</v>
       </c>
       <c r="E18" s="14">
-        <v>-20</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="15">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G18" s="15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H18" s="14">
-        <v>16.666666666666</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="I18" s="15">
         <v>27</v>
       </c>
       <c r="J18" s="15">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="K18" s="14">
-        <v>-12.903225806451</v>
+        <v>-25</v>
       </c>
       <c r="L18" s="14">
-        <v>-10</v>
+        <v>-28.947368421052</v>
       </c>
       <c r="M18" s="14">
-        <v>-28.947368421052</v>
+        <v>-34.146341463414</v>
       </c>
       <c r="N18" s="14">
-        <v>-92.582417582417</v>
+        <v>-93.25</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="D19" s="15">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="E19" s="14">
-        <v>-20.454545454545</v>
+        <v>-32.432432432432</v>
       </c>
       <c r="F19" s="15">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G19" s="15">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="H19" s="14">
-        <v>-5.755395683453</v>
+        <v>-11.034482758620</v>
       </c>
       <c r="I19" s="15">
-        <v>286</v>
+        <v>311</v>
       </c>
       <c r="J19" s="15">
-        <v>294</v>
+        <v>331</v>
       </c>
       <c r="K19" s="14">
-        <v>-2.721088435374</v>
+        <v>-6.042296072507</v>
       </c>
       <c r="L19" s="14">
-        <v>-1.718213058419</v>
+        <v>-3.115264797507</v>
       </c>
       <c r="M19" s="14">
-        <v>12.598425196850</v>
+        <v>9.507042253521</v>
       </c>
       <c r="N19" s="14">
-        <v>-74.734982332155</v>
+        <v>-75.238853503184</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,7 +1101,7 @@
         <v>20</v>
       </c>
       <c r="D20" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20" s="14">
         <v>-100</v>
@@ -1110,7 +1110,7 @@
         <v>20</v>
       </c>
       <c r="G20" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H20" s="14">
         <v>-100</v>
@@ -1119,19 +1119,19 @@
         <v>4</v>
       </c>
       <c r="J20" s="15">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K20" s="14">
-        <v>-55.555555555555</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="L20" s="14">
         <v>-42.857142857142</v>
       </c>
       <c r="M20" s="14">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="N20" s="14">
-        <v>-94.936708860759</v>
+        <v>-95.698924731182</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="D21" s="17">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="E21" s="18">
-        <v>-25</v>
+        <v>-38.181818181818</v>
       </c>
       <c r="F21" s="17">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="G21" s="17">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="H21" s="18">
-        <v>-7.881773399014</v>
+        <v>-17.452830188679</v>
       </c>
       <c r="I21" s="17">
-        <v>391</v>
+        <v>425</v>
       </c>
       <c r="J21" s="17">
-        <v>431</v>
+        <v>486</v>
       </c>
       <c r="K21" s="18">
-        <v>-9.280742459396</v>
+        <v>-12.551440329218</v>
       </c>
       <c r="L21" s="18">
-        <v>-1.262626262626</v>
+        <v>-3.628117913832</v>
       </c>
       <c r="M21" s="18">
-        <v>11.396011396011</v>
+        <v>8.695652173913</v>
       </c>
       <c r="N21" s="18">
-        <v>-79.023605150214</v>
+        <v>-79.567307692307</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>29</v>
       </c>
       <c r="C22" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D22" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E22" s="14">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="F22" s="15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G22" s="15">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H22" s="14">
-        <v>-22.222222222222</v>
+        <v>0</v>
       </c>
       <c r="I22" s="15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J22" s="15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K22" s="14">
-        <v>-7.692307692307</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="L22" s="14">
         <v>0</v>
       </c>
       <c r="M22" s="14">
-        <v>33.333333333333</v>
+        <v>18.181818181818</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1247,8 +1247,8 @@
       <c r="K23" s="14">
         <v>-100</v>
       </c>
-      <c r="L23" s="13" t="s">
-        <v>21</v>
+      <c r="L23" s="14">
+        <v>-100</v>
       </c>
       <c r="M23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D24" s="15">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E24" s="14">
-        <v>-27.272727272727</v>
+        <v>-22.448979591836</v>
       </c>
       <c r="F24" s="15">
         <v>179</v>
       </c>
       <c r="G24" s="15">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="H24" s="14">
-        <v>1.704545454545</v>
+        <v>0</v>
       </c>
       <c r="I24" s="15">
-        <v>386</v>
+        <v>424</v>
       </c>
       <c r="J24" s="15">
-        <v>400</v>
+        <v>449</v>
       </c>
       <c r="K24" s="14">
-        <v>-3.5</v>
+        <v>-5.567928730512</v>
       </c>
       <c r="L24" s="14">
-        <v>-19.750519750519</v>
+        <v>-21.915285451197</v>
       </c>
       <c r="M24" s="14">
-        <v>43.494423791821</v>
+        <v>39.473684210526</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,31 +1306,31 @@
         <v>35</v>
       </c>
       <c r="D25" s="15">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E25" s="14">
-        <v>-20.454545454545</v>
+        <v>-12.5</v>
       </c>
       <c r="F25" s="15">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G25" s="15">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="H25" s="14">
-        <v>-6.989247311827</v>
+        <v>-2.298850574712</v>
       </c>
       <c r="I25" s="15">
-        <v>367</v>
+        <v>402</v>
       </c>
       <c r="J25" s="15">
-        <v>413</v>
+        <v>453</v>
       </c>
       <c r="K25" s="14">
-        <v>-11.138014527845</v>
+        <v>-11.258278145695</v>
       </c>
       <c r="L25" s="14">
-        <v>-22.410147991543</v>
+        <v>-24.293785310734</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D26" s="15">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E26" s="14">
-        <v>-21.428571428571</v>
+        <v>-15.789473684210</v>
       </c>
       <c r="F26" s="15">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="G26" s="15">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="H26" s="14">
-        <v>-20</v>
+        <v>-10.526315789473</v>
       </c>
       <c r="I26" s="15">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="J26" s="15">
-        <v>95</v>
+        <v>114</v>
       </c>
       <c r="K26" s="14">
-        <v>3.157894736842</v>
+        <v>0.877192982456</v>
       </c>
       <c r="L26" s="14">
-        <v>-3.921568627450</v>
+        <v>4.545454545454</v>
       </c>
       <c r="M26" s="14">
-        <v>28.947368421052</v>
+        <v>29.213483146067</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,32 +1387,32 @@
       <c r="C27" s="15">
         <v>1</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="15">
+        <v>1</v>
+      </c>
+      <c r="E27" s="14">
+        <v>0</v>
       </c>
       <c r="F27" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G27" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H27" s="14">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I27" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J27" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K27" s="14">
-        <v>-57.142857142857</v>
+        <v>-50</v>
       </c>
       <c r="L27" s="14">
-        <v>200</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" s="15">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E28" s="14">
-        <v>-80</v>
+        <v>0</v>
       </c>
       <c r="F28" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G28" s="15">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H28" s="14">
-        <v>-60</v>
+        <v>-50</v>
       </c>
       <c r="I28" s="15">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J28" s="15">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K28" s="14">
-        <v>-39.285714285714</v>
+        <v>-36.666666666666</v>
       </c>
       <c r="L28" s="14">
-        <v>183.333333333333</v>
+        <v>216.666666666667</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1496,8 +1496,8 @@
       <c r="L29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="M29" s="13" t="s">
-        <v>21</v>
+      <c r="M29" s="14">
+        <v>-100</v>
       </c>
       <c r="N29" s="14">
         <v>-100</v>
@@ -1537,8 +1537,8 @@
       <c r="L30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="M30" s="13" t="s">
-        <v>21</v>
+      <c r="M30" s="14">
+        <v>-100</v>
       </c>
       <c r="N30" s="14">
         <v>-100</v>
@@ -1551,32 +1551,32 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F31" s="15">
+      <c r="D31" s="15">
         <v>1</v>
       </c>
-      <c r="G31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>21</v>
+      <c r="E31" s="14">
+        <v>-100</v>
+      </c>
+      <c r="F31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G31" s="15">
+        <v>1</v>
+      </c>
+      <c r="H31" s="14">
+        <v>-100</v>
       </c>
       <c r="I31" s="15">
         <v>2</v>
       </c>
       <c r="J31" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K31" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L31" s="14">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1610,11 +1610,11 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="15">
-        <v>1</v>
-      </c>
-      <c r="E33" s="14">
-        <v>-100</v>
+      <c r="D33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-018pct.xlsx
+++ b/data/source/weekly/cs-en-us-018pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -892,41 +892,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="15">
-        <v>1</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="15">
         <v>1</v>
       </c>
       <c r="E15" s="14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F15" s="15">
         <v>3</v>
       </c>
       <c r="G15" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" s="14">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="I15" s="15">
         <v>4</v>
       </c>
       <c r="J15" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K15" s="14">
-        <v>-42.857142857142</v>
+        <v>-50</v>
       </c>
       <c r="L15" s="14">
         <v>100</v>
       </c>
       <c r="M15" s="14">
-        <v>-42.857142857142</v>
+        <v>-50</v>
       </c>
       <c r="N15" s="14">
-        <v>-60</v>
+        <v>-66.666666666666</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D16" s="15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E16" s="14">
-        <v>-20</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F16" s="15">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G16" s="15">
         <v>20</v>
       </c>
       <c r="H16" s="14">
-        <v>-35</v>
+        <v>-25</v>
       </c>
       <c r="I16" s="15">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="J16" s="15">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K16" s="14">
-        <v>-37.777777777777</v>
+        <v>-31.25</v>
       </c>
       <c r="L16" s="14">
-        <v>-26.315789473684</v>
+        <v>-25</v>
       </c>
       <c r="M16" s="14">
-        <v>12</v>
+        <v>17.857142857142</v>
       </c>
       <c r="N16" s="14">
-        <v>-88.429752066115</v>
+        <v>-87.452471482889</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D17" s="15">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E17" s="14">
-        <v>-20</v>
+        <v>-30</v>
       </c>
       <c r="F17" s="15">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="G17" s="15">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H17" s="14">
-        <v>-26.923076923076</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="I17" s="15">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="J17" s="15">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="K17" s="14">
-        <v>-8.928571428571</v>
+        <v>-4.545454545454</v>
       </c>
       <c r="L17" s="14">
-        <v>50</v>
+        <v>61.538461538461</v>
       </c>
       <c r="M17" s="14">
-        <v>121.739130434783</v>
+        <v>125</v>
       </c>
       <c r="N17" s="14">
-        <v>-32</v>
+        <v>-22.222222222222</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="15">
+        <v>5</v>
       </c>
       <c r="D18" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E18" s="14">
-        <v>-100</v>
+        <v>25</v>
       </c>
       <c r="F18" s="15">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G18" s="15">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H18" s="14">
-        <v>-15.384615384615</v>
+        <v>-17.647058823529</v>
       </c>
       <c r="I18" s="15">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="J18" s="15">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="K18" s="14">
-        <v>-25</v>
+        <v>-17.5</v>
       </c>
       <c r="L18" s="14">
-        <v>-28.947368421052</v>
+        <v>-17.5</v>
       </c>
       <c r="M18" s="14">
-        <v>-34.146341463414</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="N18" s="14">
-        <v>-93.25</v>
+        <v>-92.5</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D19" s="15">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E19" s="14">
-        <v>-32.432432432432</v>
+        <v>-2.941176470588</v>
       </c>
       <c r="F19" s="15">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G19" s="15">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H19" s="14">
-        <v>-11.034482758620</v>
+        <v>-12.925170068027</v>
       </c>
       <c r="I19" s="15">
-        <v>311</v>
+        <v>344</v>
       </c>
       <c r="J19" s="15">
-        <v>331</v>
+        <v>365</v>
       </c>
       <c r="K19" s="14">
-        <v>-6.042296072507</v>
+        <v>-5.753424657534</v>
       </c>
       <c r="L19" s="14">
-        <v>-3.115264797507</v>
+        <v>-4.178272980501</v>
       </c>
       <c r="M19" s="14">
-        <v>9.507042253521</v>
+        <v>12.418300653594</v>
       </c>
       <c r="N19" s="14">
-        <v>-75.238853503184</v>
+        <v>-75.036284470246</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
+      <c r="C20" s="15">
+        <v>2</v>
       </c>
       <c r="D20" s="15">
         <v>2</v>
       </c>
       <c r="E20" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F20" s="13" t="s">
-        <v>20</v>
+        <v>0</v>
+      </c>
+      <c r="F20" s="15">
+        <v>2</v>
       </c>
       <c r="G20" s="15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H20" s="14">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I20" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J20" s="15">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K20" s="14">
-        <v>-63.636363636363</v>
+        <v>-53.846153846153</v>
       </c>
       <c r="L20" s="14">
-        <v>-42.857142857142</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="M20" s="14">
-        <v>-50</v>
+        <v>-25</v>
       </c>
       <c r="N20" s="14">
-        <v>-95.698924731182</v>
+        <v>-93.877551020408</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="D21" s="17">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E21" s="18">
-        <v>-38.181818181818</v>
+        <v>-3.703703703703</v>
       </c>
       <c r="F21" s="17">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="G21" s="17">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="H21" s="18">
-        <v>-17.452830188679</v>
+        <v>-14.414414414414</v>
       </c>
       <c r="I21" s="17">
-        <v>425</v>
+        <v>483</v>
       </c>
       <c r="J21" s="17">
-        <v>486</v>
+        <v>540</v>
       </c>
       <c r="K21" s="18">
-        <v>-12.551440329218</v>
+        <v>-10.555555555555</v>
       </c>
       <c r="L21" s="18">
-        <v>-3.628117913832</v>
+        <v>-1.829268292682</v>
       </c>
       <c r="M21" s="18">
-        <v>8.695652173913</v>
+        <v>13.380281690140</v>
       </c>
       <c r="N21" s="18">
-        <v>-79.567307692307</v>
+        <v>-78.787878787878</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1183,10 +1183,10 @@
         <v>1</v>
       </c>
       <c r="D22" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E22" s="14">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F22" s="15">
         <v>6</v>
@@ -1198,19 +1198,19 @@
         <v>0</v>
       </c>
       <c r="I22" s="15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J22" s="15">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K22" s="14">
-        <v>-7.142857142857</v>
+        <v>-12.5</v>
       </c>
       <c r="L22" s="14">
-        <v>0</v>
+        <v>-17.647058823529</v>
       </c>
       <c r="M22" s="14">
-        <v>18.181818181818</v>
+        <v>7.692307692307</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="D24" s="15">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E24" s="14">
-        <v>-22.448979591836</v>
+        <v>4.347826086956</v>
       </c>
       <c r="F24" s="15">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="G24" s="15">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="H24" s="14">
-        <v>0</v>
+        <v>-9.574468085106</v>
       </c>
       <c r="I24" s="15">
-        <v>424</v>
+        <v>471</v>
       </c>
       <c r="J24" s="15">
-        <v>449</v>
+        <v>495</v>
       </c>
       <c r="K24" s="14">
-        <v>-5.567928730512</v>
+        <v>-4.848484848484</v>
       </c>
       <c r="L24" s="14">
-        <v>-21.915285451197</v>
+        <v>-20.439189189189</v>
       </c>
       <c r="M24" s="14">
-        <v>39.473684210526</v>
+        <v>42.727272727272</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D25" s="15">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E25" s="14">
-        <v>-12.5</v>
+        <v>-4.444444444444</v>
       </c>
       <c r="F25" s="15">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="G25" s="15">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H25" s="14">
-        <v>-2.298850574712</v>
+        <v>-6.857142857142</v>
       </c>
       <c r="I25" s="15">
-        <v>402</v>
+        <v>444</v>
       </c>
       <c r="J25" s="15">
-        <v>453</v>
+        <v>498</v>
       </c>
       <c r="K25" s="14">
-        <v>-11.258278145695</v>
+        <v>-10.843373493975</v>
       </c>
       <c r="L25" s="14">
-        <v>-24.293785310734</v>
+        <v>-23.972602739726</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D26" s="15">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E26" s="14">
-        <v>-15.789473684210</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F26" s="15">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="G26" s="15">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H26" s="14">
-        <v>-10.526315789473</v>
+        <v>5.357142857142</v>
       </c>
       <c r="I26" s="15">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="J26" s="15">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="K26" s="14">
-        <v>0.877192982456</v>
+        <v>3.968253968253</v>
       </c>
       <c r="L26" s="14">
-        <v>4.545454545454</v>
+        <v>4.8</v>
       </c>
       <c r="M26" s="14">
-        <v>29.213483146067</v>
+        <v>39.361702127659</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,32 +1384,32 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="15">
-        <v>1</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="15">
         <v>1</v>
       </c>
       <c r="E27" s="14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F27" s="15">
         <v>3</v>
       </c>
       <c r="G27" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H27" s="14">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="I27" s="15">
         <v>4</v>
       </c>
       <c r="J27" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K27" s="14">
-        <v>-50</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="L27" s="14">
         <v>33.333333333333</v>
@@ -1429,31 +1429,31 @@
         <v>2</v>
       </c>
       <c r="D28" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E28" s="14">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F28" s="15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G28" s="15">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H28" s="14">
         <v>-50</v>
       </c>
       <c r="I28" s="15">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J28" s="15">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K28" s="14">
-        <v>-36.666666666666</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="L28" s="14">
-        <v>216.666666666667</v>
+        <v>162.5</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1551,11 +1551,11 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="15">
-        <v>1</v>
-      </c>
-      <c r="E31" s="14">
-        <v>-100</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
@@ -1620,7 +1620,7 @@
         <v>20</v>
       </c>
       <c r="G33" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H33" s="14">
         <v>-100</v>

--- a/data/source/weekly/cs-en-us-018pct.xlsx
+++ b/data/source/weekly/cs-en-us-018pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -902,22 +902,22 @@
         <v>-100</v>
       </c>
       <c r="F15" s="15">
+        <v>2</v>
+      </c>
+      <c r="G15" s="15">
         <v>3</v>
       </c>
-      <c r="G15" s="15">
-        <v>2</v>
-      </c>
       <c r="H15" s="14">
-        <v>50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I15" s="15">
         <v>4</v>
       </c>
       <c r="J15" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K15" s="14">
-        <v>-50</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="L15" s="14">
         <v>100</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D16" s="15">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E16" s="14">
-        <v>66.666666666666</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F16" s="15">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G16" s="15">
         <v>20</v>
       </c>
       <c r="H16" s="14">
-        <v>-25</v>
+        <v>-5</v>
       </c>
       <c r="I16" s="15">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="J16" s="15">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="K16" s="14">
-        <v>-31.25</v>
+        <v>-29.090909090909</v>
       </c>
       <c r="L16" s="14">
-        <v>-25</v>
+        <v>-20.408163265306</v>
       </c>
       <c r="M16" s="14">
-        <v>17.857142857142</v>
+        <v>30</v>
       </c>
       <c r="N16" s="14">
-        <v>-87.452471482889</v>
+        <v>-86.505190311418</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D17" s="15">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E17" s="14">
-        <v>-30</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F17" s="15">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G17" s="15">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H17" s="14">
-        <v>-6.666666666666</v>
+        <v>-7.407407407407</v>
       </c>
       <c r="I17" s="15">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="J17" s="15">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="K17" s="14">
-        <v>-4.545454545454</v>
+        <v>0</v>
       </c>
       <c r="L17" s="14">
-        <v>61.538461538461</v>
+        <v>64.285714285714</v>
       </c>
       <c r="M17" s="14">
-        <v>125</v>
+        <v>146.428571428571</v>
       </c>
       <c r="N17" s="14">
-        <v>-22.222222222222</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D18" s="15">
         <v>4</v>
       </c>
       <c r="E18" s="14">
-        <v>25</v>
+        <v>-25</v>
       </c>
       <c r="F18" s="15">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G18" s="15">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H18" s="14">
-        <v>-17.647058823529</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I18" s="15">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J18" s="15">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="K18" s="14">
-        <v>-17.5</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="L18" s="14">
-        <v>-17.5</v>
+        <v>-16.279069767441</v>
       </c>
       <c r="M18" s="14">
-        <v>-26.666666666666</v>
+        <v>-23.404255319148</v>
       </c>
       <c r="N18" s="14">
-        <v>-92.5</v>
+        <v>-92.324093816631</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,37 +1060,37 @@
         <v>33</v>
       </c>
       <c r="D19" s="15">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="E19" s="14">
-        <v>-2.941176470588</v>
+        <v>-29.787234042553</v>
       </c>
       <c r="F19" s="15">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="G19" s="15">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="H19" s="14">
-        <v>-12.925170068027</v>
+        <v>-24.074074074074</v>
       </c>
       <c r="I19" s="15">
-        <v>344</v>
+        <v>376</v>
       </c>
       <c r="J19" s="15">
-        <v>365</v>
+        <v>412</v>
       </c>
       <c r="K19" s="14">
-        <v>-5.753424657534</v>
+        <v>-8.737864077669</v>
       </c>
       <c r="L19" s="14">
-        <v>-4.178272980501</v>
+        <v>-5.527638190954</v>
       </c>
       <c r="M19" s="14">
-        <v>12.418300653594</v>
+        <v>11.904761904761</v>
       </c>
       <c r="N19" s="14">
-        <v>-75.036284470246</v>
+        <v>-75.115817339510</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,37 +1101,37 @@
         <v>2</v>
       </c>
       <c r="D20" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F20" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G20" s="15">
         <v>6</v>
       </c>
       <c r="H20" s="14">
-        <v>-66.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I20" s="15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J20" s="15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K20" s="14">
-        <v>-53.846153846153</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="L20" s="14">
-        <v>-14.285714285714</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="M20" s="14">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="N20" s="14">
-        <v>-93.877551020408</v>
+        <v>-92.660550458715</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D21" s="17">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="E21" s="18">
-        <v>-3.703703703703</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="F21" s="17">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="G21" s="17">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="H21" s="18">
-        <v>-14.414414414414</v>
+        <v>-21.610169491525</v>
       </c>
       <c r="I21" s="17">
-        <v>483</v>
+        <v>532</v>
       </c>
       <c r="J21" s="17">
-        <v>540</v>
+        <v>603</v>
       </c>
       <c r="K21" s="18">
-        <v>-10.555555555555</v>
+        <v>-11.774461028192</v>
       </c>
       <c r="L21" s="18">
-        <v>-1.829268292682</v>
+        <v>-2.205882352941</v>
       </c>
       <c r="M21" s="18">
-        <v>13.380281690140</v>
+        <v>15.652173913043</v>
       </c>
       <c r="N21" s="18">
-        <v>-78.787878787878</v>
+        <v>-78.608765581021</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="15">
-        <v>1</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E22" s="14">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="F22" s="15">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G22" s="15">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H22" s="14">
-        <v>0</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="I22" s="15">
         <v>14</v>
       </c>
       <c r="J22" s="15">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K22" s="14">
-        <v>-12.5</v>
+        <v>-26.315789473684</v>
       </c>
       <c r="L22" s="14">
-        <v>-17.647058823529</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="M22" s="14">
-        <v>7.692307692307</v>
+        <v>0</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D24" s="15">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="E24" s="14">
-        <v>4.347826086956</v>
+        <v>-27.941176470588</v>
       </c>
       <c r="F24" s="15">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="G24" s="15">
-        <v>188</v>
+        <v>207</v>
       </c>
       <c r="H24" s="14">
-        <v>-9.574468085106</v>
+        <v>-19.323671497584</v>
       </c>
       <c r="I24" s="15">
-        <v>471</v>
+        <v>519</v>
       </c>
       <c r="J24" s="15">
-        <v>495</v>
+        <v>563</v>
       </c>
       <c r="K24" s="14">
-        <v>-4.848484848484</v>
+        <v>-7.815275310834</v>
       </c>
       <c r="L24" s="14">
-        <v>-20.439189189189</v>
+        <v>-20.642201834862</v>
       </c>
       <c r="M24" s="14">
-        <v>42.727272727272</v>
+        <v>39.892183288409</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="D25" s="15">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="E25" s="14">
-        <v>-4.444444444444</v>
+        <v>-13.114754098360</v>
       </c>
       <c r="F25" s="15">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="G25" s="15">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="H25" s="14">
-        <v>-6.857142857142</v>
+        <v>-12.631578947368</v>
       </c>
       <c r="I25" s="15">
-        <v>444</v>
+        <v>496</v>
       </c>
       <c r="J25" s="15">
-        <v>498</v>
+        <v>559</v>
       </c>
       <c r="K25" s="14">
-        <v>-10.843373493975</v>
+        <v>-11.270125223613</v>
       </c>
       <c r="L25" s="14">
-        <v>-23.972602739726</v>
+        <v>-23.456790123456</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D26" s="15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E26" s="14">
-        <v>66.666666666666</v>
+        <v>38.461538461538</v>
       </c>
       <c r="F26" s="15">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G26" s="15">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H26" s="14">
-        <v>5.357142857142</v>
+        <v>3.448275862068</v>
       </c>
       <c r="I26" s="15">
-        <v>131</v>
+        <v>148</v>
       </c>
       <c r="J26" s="15">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="K26" s="14">
-        <v>3.968253968253</v>
+        <v>6.474820143884</v>
       </c>
       <c r="L26" s="14">
-        <v>4.8</v>
+        <v>8.823529411764</v>
       </c>
       <c r="M26" s="14">
-        <v>39.361702127659</v>
+        <v>42.307692307692</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1394,22 +1394,22 @@
         <v>-100</v>
       </c>
       <c r="F27" s="15">
+        <v>2</v>
+      </c>
+      <c r="G27" s="15">
         <v>3</v>
       </c>
-      <c r="G27" s="15">
-        <v>2</v>
-      </c>
       <c r="H27" s="14">
-        <v>50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I27" s="15">
         <v>4</v>
       </c>
       <c r="J27" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K27" s="14">
-        <v>-55.555555555555</v>
+        <v>-60</v>
       </c>
       <c r="L27" s="14">
         <v>33.333333333333</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="15">
-        <v>2</v>
-      </c>
-      <c r="D28" s="15">
-        <v>3</v>
-      </c>
-      <c r="E28" s="14">
-        <v>-33.333333333333</v>
+        <v>1</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="15">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G28" s="15">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="H28" s="14">
-        <v>-50</v>
+        <v>-40</v>
       </c>
       <c r="I28" s="15">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J28" s="15">
         <v>33</v>
       </c>
       <c r="K28" s="14">
-        <v>-36.363636363636</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L28" s="14">
-        <v>162.5</v>
+        <v>83.333333333333</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-018pct.xlsx
+++ b/data/source/weekly/cs-en-us-018pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -895,20 +895,20 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="15">
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="15">
         <v>1</v>
-      </c>
-      <c r="E15" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F15" s="15">
-        <v>2</v>
       </c>
       <c r="G15" s="15">
         <v>3</v>
       </c>
       <c r="H15" s="14">
-        <v>-33.333333333333</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I15" s="15">
         <v>4</v>
@@ -920,7 +920,7 @@
         <v>-55.555555555555</v>
       </c>
       <c r="L15" s="14">
-        <v>100</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M15" s="14">
         <v>-50</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D16" s="15">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E16" s="14">
-        <v>-14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="F16" s="15">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G16" s="15">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H16" s="14">
-        <v>-5</v>
+        <v>-5.555555555555</v>
       </c>
       <c r="I16" s="15">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J16" s="15">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K16" s="14">
-        <v>-29.090909090909</v>
+        <v>-29.310344827586</v>
       </c>
       <c r="L16" s="14">
-        <v>-20.408163265306</v>
+        <v>-24.074074074074</v>
       </c>
       <c r="M16" s="14">
-        <v>30</v>
+        <v>36.666666666666</v>
       </c>
       <c r="N16" s="14">
-        <v>-86.505190311418</v>
+        <v>-86.774193548387</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D17" s="15">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E17" s="14">
-        <v>66.666666666666</v>
+        <v>100</v>
       </c>
       <c r="F17" s="15">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="G17" s="15">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H17" s="14">
-        <v>-7.407407407407</v>
+        <v>37.5</v>
       </c>
       <c r="I17" s="15">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="J17" s="15">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="K17" s="14">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L17" s="14">
-        <v>64.285714285714</v>
+        <v>76.086956521739</v>
       </c>
       <c r="M17" s="14">
-        <v>146.428571428571</v>
+        <v>145.454545454545</v>
       </c>
       <c r="N17" s="14">
-        <v>-25</v>
+        <v>-20.588235294117</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,37 +1019,37 @@
         <v>3</v>
       </c>
       <c r="D18" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E18" s="14">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="F18" s="15">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G18" s="15">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H18" s="14">
-        <v>-33.333333333333</v>
+        <v>-31.25</v>
       </c>
       <c r="I18" s="15">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="J18" s="15">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K18" s="14">
-        <v>-18.181818181818</v>
+        <v>-17.021276595744</v>
       </c>
       <c r="L18" s="14">
-        <v>-16.279069767441</v>
+        <v>-9.302325581395</v>
       </c>
       <c r="M18" s="14">
-        <v>-23.404255319148</v>
+        <v>-22</v>
       </c>
       <c r="N18" s="14">
-        <v>-92.324093816631</v>
+        <v>-92.427184466019</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D19" s="15">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="E19" s="14">
-        <v>-29.787234042553</v>
+        <v>-8.823529411764</v>
       </c>
       <c r="F19" s="15">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G19" s="15">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="H19" s="14">
-        <v>-24.074074074074</v>
+        <v>-21.052631578947</v>
       </c>
       <c r="I19" s="15">
-        <v>376</v>
+        <v>407</v>
       </c>
       <c r="J19" s="15">
-        <v>412</v>
+        <v>446</v>
       </c>
       <c r="K19" s="14">
-        <v>-8.737864077669</v>
+        <v>-8.744394618834</v>
       </c>
       <c r="L19" s="14">
-        <v>-5.527638190954</v>
+        <v>-4.460093896713</v>
       </c>
       <c r="M19" s="14">
-        <v>11.904761904761</v>
+        <v>12.430939226519</v>
       </c>
       <c r="N19" s="14">
-        <v>-75.115817339510</v>
+        <v>-75.152625152625</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
+        <v>1</v>
+      </c>
+      <c r="D20" s="15">
         <v>2</v>
       </c>
-      <c r="D20" s="15">
-        <v>1</v>
-      </c>
       <c r="E20" s="14">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="F20" s="15">
         <v>4</v>
       </c>
       <c r="G20" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H20" s="14">
-        <v>-33.333333333333</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="I20" s="15">
         <v>8</v>
       </c>
       <c r="J20" s="15">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K20" s="14">
-        <v>-42.857142857142</v>
+        <v>-50</v>
       </c>
       <c r="L20" s="14">
         <v>-11.111111111111</v>
       </c>
       <c r="M20" s="14">
-        <v>0</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="N20" s="14">
-        <v>-92.660550458715</v>
+        <v>-93.162393162393</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D21" s="17">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="E21" s="18">
-        <v>-22.222222222222</v>
+        <v>4.166666666666</v>
       </c>
       <c r="F21" s="17">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G21" s="17">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="H21" s="18">
-        <v>-21.610169491525</v>
+        <v>-15.454545454545</v>
       </c>
       <c r="I21" s="17">
-        <v>532</v>
+        <v>580</v>
       </c>
       <c r="J21" s="17">
-        <v>603</v>
+        <v>651</v>
       </c>
       <c r="K21" s="18">
-        <v>-11.774461028192</v>
+        <v>-10.906298003072</v>
       </c>
       <c r="L21" s="18">
-        <v>-2.205882352941</v>
+        <v>-0.343642611683</v>
       </c>
       <c r="M21" s="18">
-        <v>15.652173913043</v>
+        <v>17.171717171717</v>
       </c>
       <c r="N21" s="18">
-        <v>-78.608765581021</v>
+        <v>-78.510559466469</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="15">
+        <v>2</v>
       </c>
       <c r="D22" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E22" s="14">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="F22" s="15">
         <v>4</v>
       </c>
       <c r="G22" s="15">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H22" s="14">
-        <v>-55.555555555555</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="I22" s="15">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J22" s="15">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K22" s="14">
-        <v>-26.315789473684</v>
+        <v>-20</v>
       </c>
       <c r="L22" s="14">
-        <v>-22.222222222222</v>
+        <v>-15.789473684210</v>
       </c>
       <c r="M22" s="14">
-        <v>0</v>
+        <v>6.666666666666</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="D24" s="15">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="E24" s="14">
-        <v>-27.941176470588</v>
+        <v>12.068965517241</v>
       </c>
       <c r="F24" s="15">
-        <v>167</v>
+        <v>203</v>
       </c>
       <c r="G24" s="15">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="H24" s="14">
-        <v>-19.323671497584</v>
+        <v>-8.144796380090</v>
       </c>
       <c r="I24" s="15">
-        <v>519</v>
+        <v>587</v>
       </c>
       <c r="J24" s="15">
-        <v>563</v>
+        <v>621</v>
       </c>
       <c r="K24" s="14">
-        <v>-7.815275310834</v>
+        <v>-5.475040257648</v>
       </c>
       <c r="L24" s="14">
-        <v>-20.642201834862</v>
+        <v>-15.660919540229</v>
       </c>
       <c r="M24" s="14">
-        <v>39.892183288409</v>
+        <v>46.384039900249</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D25" s="15">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E25" s="14">
-        <v>-13.114754098360</v>
+        <v>-17.741935483871</v>
       </c>
       <c r="F25" s="15">
-        <v>166</v>
+        <v>185</v>
       </c>
       <c r="G25" s="15">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="H25" s="14">
-        <v>-12.631578947368</v>
+        <v>-11.057692307692</v>
       </c>
       <c r="I25" s="15">
-        <v>496</v>
+        <v>550</v>
       </c>
       <c r="J25" s="15">
-        <v>559</v>
+        <v>621</v>
       </c>
       <c r="K25" s="14">
-        <v>-11.270125223613</v>
+        <v>-11.433172302737</v>
       </c>
       <c r="L25" s="14">
-        <v>-23.456790123456</v>
+        <v>-20.977011494252</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D26" s="15">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E26" s="14">
-        <v>38.461538461538</v>
+        <v>31.578947368421</v>
       </c>
       <c r="F26" s="15">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="G26" s="15">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H26" s="14">
-        <v>3.448275862068</v>
+        <v>19.047619047619</v>
       </c>
       <c r="I26" s="15">
-        <v>148</v>
+        <v>174</v>
       </c>
       <c r="J26" s="15">
-        <v>139</v>
+        <v>158</v>
       </c>
       <c r="K26" s="14">
-        <v>6.474820143884</v>
+        <v>10.126582278481</v>
       </c>
       <c r="L26" s="14">
-        <v>8.823529411764</v>
+        <v>15.231788079470</v>
       </c>
       <c r="M26" s="14">
-        <v>42.307692307692</v>
+        <v>48.717948717948</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,20 +1387,20 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="15">
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="15">
         <v>1</v>
-      </c>
-      <c r="E27" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F27" s="15">
-        <v>2</v>
       </c>
       <c r="G27" s="15">
         <v>3</v>
       </c>
       <c r="H27" s="14">
-        <v>-33.333333333333</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I27" s="15">
         <v>4</v>
@@ -1412,7 +1412,7 @@
         <v>-60</v>
       </c>
       <c r="L27" s="14">
-        <v>33.333333333333</v>
+        <v>-20</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,7 +1426,7 @@
         <v>35</v>
       </c>
       <c r="C28" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>20</v>
@@ -1435,25 +1435,25 @@
         <v>21</v>
       </c>
       <c r="F28" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G28" s="15">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H28" s="14">
-        <v>-40</v>
+        <v>40</v>
       </c>
       <c r="I28" s="15">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J28" s="15">
         <v>33</v>
       </c>
       <c r="K28" s="14">
-        <v>-33.333333333333</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="L28" s="14">
-        <v>83.333333333333</v>
+        <v>100</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1548,8 +1548,8 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
+      <c r="C31" s="15">
+        <v>1</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1557,26 +1557,26 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
+      <c r="F31" s="15">
+        <v>2</v>
       </c>
       <c r="G31" s="15">
         <v>1</v>
       </c>
       <c r="H31" s="14">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="I31" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J31" s="15">
         <v>2</v>
       </c>
       <c r="K31" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L31" s="14">
-        <v>-33.333333333333</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1619,11 +1619,11 @@
       <c r="F33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G33" s="15">
-        <v>1</v>
-      </c>
-      <c r="H33" s="14">
-        <v>-100</v>
+      <c r="G33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-018pct.xlsx
+++ b/data/source/weekly/cs-en-us-018pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -895,29 +895,29 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F15" s="15">
+      <c r="D15" s="15">
         <v>1</v>
+      </c>
+      <c r="E15" s="14">
+        <v>-100</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G15" s="15">
         <v>3</v>
       </c>
       <c r="H15" s="14">
-        <v>-66.666666666666</v>
+        <v>-100</v>
       </c>
       <c r="I15" s="15">
         <v>4</v>
       </c>
       <c r="J15" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K15" s="14">
-        <v>-55.555555555555</v>
+        <v>-60</v>
       </c>
       <c r="L15" s="14">
         <v>33.333333333333</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D16" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E16" s="14">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="F16" s="15">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G16" s="15">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H16" s="14">
-        <v>-5.555555555555</v>
+        <v>57.142857142857</v>
       </c>
       <c r="I16" s="15">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="J16" s="15">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K16" s="14">
-        <v>-29.310344827586</v>
+        <v>-15.254237288135</v>
       </c>
       <c r="L16" s="14">
-        <v>-24.074074074074</v>
+        <v>-13.793103448275</v>
       </c>
       <c r="M16" s="14">
-        <v>36.666666666666</v>
+        <v>56.25</v>
       </c>
       <c r="N16" s="14">
-        <v>-86.774193548387</v>
+        <v>-84.848484848484</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D17" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E17" s="14">
-        <v>100</v>
+        <v>14.285714285714</v>
       </c>
       <c r="F17" s="15">
         <v>33</v>
       </c>
       <c r="G17" s="15">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H17" s="14">
-        <v>37.5</v>
+        <v>26.923076923076</v>
       </c>
       <c r="I17" s="15">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="J17" s="15">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="K17" s="14">
-        <v>8</v>
+        <v>8.536585365853</v>
       </c>
       <c r="L17" s="14">
-        <v>76.086956521739</v>
+        <v>61.818181818181</v>
       </c>
       <c r="M17" s="14">
-        <v>145.454545454545</v>
+        <v>154.285714285714</v>
       </c>
       <c r="N17" s="14">
-        <v>-20.588235294117</v>
+        <v>-22.608695652173</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D18" s="15">
         <v>3</v>
       </c>
       <c r="E18" s="14">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F18" s="15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G18" s="15">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H18" s="14">
-        <v>-31.25</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I18" s="15">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J18" s="15">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="K18" s="14">
-        <v>-17.021276595744</v>
+        <v>-20</v>
       </c>
       <c r="L18" s="14">
-        <v>-9.302325581395</v>
+        <v>-18.367346938775</v>
       </c>
       <c r="M18" s="14">
-        <v>-22</v>
+        <v>-24.528301886792</v>
       </c>
       <c r="N18" s="14">
-        <v>-92.427184466019</v>
+        <v>-92.844364937388</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D19" s="15">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E19" s="14">
-        <v>-8.823529411764</v>
+        <v>0</v>
       </c>
       <c r="F19" s="15">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="G19" s="15">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="H19" s="14">
-        <v>-21.052631578947</v>
+        <v>-13.513513513513</v>
       </c>
       <c r="I19" s="15">
-        <v>407</v>
+        <v>440</v>
       </c>
       <c r="J19" s="15">
-        <v>446</v>
+        <v>479</v>
       </c>
       <c r="K19" s="14">
-        <v>-8.744394618834</v>
+        <v>-8.141962421711</v>
       </c>
       <c r="L19" s="14">
-        <v>-4.460093896713</v>
+        <v>-4.555314533622</v>
       </c>
       <c r="M19" s="14">
-        <v>12.430939226519</v>
+        <v>11.959287531806</v>
       </c>
       <c r="N19" s="14">
-        <v>-75.152625152625</v>
+        <v>-75.322490185081</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1107,31 +1107,31 @@
         <v>-50</v>
       </c>
       <c r="F20" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G20" s="15">
         <v>7</v>
       </c>
       <c r="H20" s="14">
-        <v>-42.857142857142</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="I20" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J20" s="15">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K20" s="14">
         <v>-50</v>
       </c>
       <c r="L20" s="14">
-        <v>-11.111111111111</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="M20" s="14">
-        <v>-11.111111111111</v>
+        <v>-10</v>
       </c>
       <c r="N20" s="14">
-        <v>-93.162393162393</v>
+        <v>-93.129770992366</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D21" s="17">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E21" s="18">
-        <v>4.166666666666</v>
+        <v>10.638297872340</v>
       </c>
       <c r="F21" s="17">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="G21" s="17">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="H21" s="18">
-        <v>-15.454545454545</v>
+        <v>-5.660377358490</v>
       </c>
       <c r="I21" s="17">
-        <v>580</v>
+        <v>632</v>
       </c>
       <c r="J21" s="17">
-        <v>651</v>
+        <v>698</v>
       </c>
       <c r="K21" s="18">
-        <v>-10.906298003072</v>
+        <v>-9.455587392550</v>
       </c>
       <c r="L21" s="18">
-        <v>-0.343642611683</v>
+        <v>-0.940438871473</v>
       </c>
       <c r="M21" s="18">
-        <v>17.171717171717</v>
+        <v>18.352059925093</v>
       </c>
       <c r="N21" s="18">
-        <v>-78.510559466469</v>
+        <v>-78.466780238500</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>29</v>
       </c>
       <c r="C22" s="15">
+        <v>1</v>
+      </c>
+      <c r="D22" s="15">
         <v>2</v>
       </c>
-      <c r="D22" s="15">
-        <v>1</v>
-      </c>
       <c r="E22" s="14">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="F22" s="15">
         <v>4</v>
       </c>
       <c r="G22" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H22" s="14">
-        <v>-42.857142857142</v>
+        <v>-50</v>
       </c>
       <c r="I22" s="15">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J22" s="15">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K22" s="14">
-        <v>-20</v>
+        <v>-22.727272727272</v>
       </c>
       <c r="L22" s="14">
-        <v>-15.789473684210</v>
+        <v>-32</v>
       </c>
       <c r="M22" s="14">
-        <v>6.666666666666</v>
+        <v>0</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,35 +1220,35 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H23" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I23" s="13" t="s">
-        <v>20</v>
+      <c r="C23" s="15">
+        <v>1</v>
+      </c>
+      <c r="D23" s="15">
+        <v>1</v>
+      </c>
+      <c r="E23" s="14">
+        <v>0</v>
+      </c>
+      <c r="F23" s="15">
+        <v>1</v>
+      </c>
+      <c r="G23" s="15">
+        <v>1</v>
+      </c>
+      <c r="H23" s="14">
+        <v>0</v>
+      </c>
+      <c r="I23" s="15">
+        <v>1</v>
       </c>
       <c r="J23" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K23" s="14">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="L23" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="D24" s="15">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="E24" s="14">
-        <v>12.068965517241</v>
+        <v>-6</v>
       </c>
       <c r="F24" s="15">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="G24" s="15">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H24" s="14">
-        <v>-8.144796380090</v>
+        <v>-2.702702702702</v>
       </c>
       <c r="I24" s="15">
-        <v>587</v>
+        <v>638</v>
       </c>
       <c r="J24" s="15">
-        <v>621</v>
+        <v>671</v>
       </c>
       <c r="K24" s="14">
-        <v>-5.475040257648</v>
+        <v>-4.918032786885</v>
       </c>
       <c r="L24" s="14">
-        <v>-15.660919540229</v>
+        <v>-14.362416107382</v>
       </c>
       <c r="M24" s="14">
-        <v>46.384039900249</v>
+        <v>49.414519906323</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="D25" s="15">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="E25" s="14">
-        <v>-17.741935483871</v>
+        <v>7.692307692307</v>
       </c>
       <c r="F25" s="15">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="G25" s="15">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H25" s="14">
-        <v>-11.057692307692</v>
+        <v>-5.797101449275</v>
       </c>
       <c r="I25" s="15">
-        <v>550</v>
+        <v>595</v>
       </c>
       <c r="J25" s="15">
-        <v>621</v>
+        <v>660</v>
       </c>
       <c r="K25" s="14">
-        <v>-11.433172302737</v>
+        <v>-9.848484848484</v>
       </c>
       <c r="L25" s="14">
-        <v>-20.977011494252</v>
+        <v>-19.811320754717</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D26" s="15">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E26" s="14">
-        <v>31.578947368421</v>
+        <v>90.909090909090</v>
       </c>
       <c r="F26" s="15">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="G26" s="15">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="H26" s="14">
-        <v>19.047619047619</v>
+        <v>56.363636363636</v>
       </c>
       <c r="I26" s="15">
-        <v>174</v>
+        <v>198</v>
       </c>
       <c r="J26" s="15">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="K26" s="14">
-        <v>10.126582278481</v>
+        <v>17.159763313609</v>
       </c>
       <c r="L26" s="14">
-        <v>15.231788079470</v>
+        <v>23.75</v>
       </c>
       <c r="M26" s="14">
-        <v>48.717948717948</v>
+        <v>54.6875</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,29 +1387,29 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F27" s="15">
+      <c r="D27" s="15">
         <v>1</v>
+      </c>
+      <c r="E27" s="14">
+        <v>-100</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G27" s="15">
         <v>3</v>
       </c>
       <c r="H27" s="14">
-        <v>-66.666666666666</v>
+        <v>-100</v>
       </c>
       <c r="I27" s="15">
         <v>4</v>
       </c>
       <c r="J27" s="15">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K27" s="14">
-        <v>-60</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="L27" s="14">
         <v>-20</v>
@@ -1426,7 +1426,7 @@
         <v>35</v>
       </c>
       <c r="C28" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>20</v>
@@ -1435,25 +1435,25 @@
         <v>21</v>
       </c>
       <c r="F28" s="15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G28" s="15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H28" s="14">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="I28" s="15">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J28" s="15">
         <v>33</v>
       </c>
       <c r="K28" s="14">
-        <v>-27.272727272727</v>
+        <v>-24.242424242424</v>
       </c>
       <c r="L28" s="14">
-        <v>100</v>
+        <v>78.571428571428</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1493,8 +1493,8 @@
       <c r="K29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L29" s="13" t="s">
-        <v>21</v>
+      <c r="L29" s="14">
+        <v>-100</v>
       </c>
       <c r="M29" s="14">
         <v>-100</v>
@@ -1534,8 +1534,8 @@
       <c r="K30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L30" s="13" t="s">
-        <v>21</v>
+      <c r="L30" s="14">
+        <v>-100</v>
       </c>
       <c r="M30" s="14">
         <v>-100</v>
@@ -1551,32 +1551,32 @@
       <c r="C31" s="15">
         <v>1</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="15">
+        <v>4</v>
+      </c>
+      <c r="E31" s="14">
+        <v>-75</v>
       </c>
       <c r="F31" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G31" s="15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H31" s="14">
-        <v>100</v>
+        <v>-25</v>
       </c>
       <c r="I31" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J31" s="15">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K31" s="14">
-        <v>100</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="L31" s="14">
-        <v>33.333333333333</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-018pct.xlsx
+++ b/data/source/weekly/cs-en-us-018pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -895,17 +895,17 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="15">
-        <v>1</v>
-      </c>
-      <c r="E15" s="14">
-        <v>-100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G15" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H15" s="14">
         <v>-100</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D16" s="15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E16" s="14">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="F16" s="15">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G16" s="15">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H16" s="14">
-        <v>57.142857142857</v>
+        <v>40</v>
       </c>
       <c r="I16" s="15">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="J16" s="15">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="K16" s="14">
-        <v>-15.254237288135</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="L16" s="14">
-        <v>-13.793103448275</v>
+        <v>-8.474576271186</v>
       </c>
       <c r="M16" s="14">
-        <v>56.25</v>
+        <v>54.285714285714</v>
       </c>
       <c r="N16" s="14">
-        <v>-84.848484848484</v>
+        <v>-84.615384615384</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D17" s="15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E17" s="14">
-        <v>14.285714285714</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="F17" s="15">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G17" s="15">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H17" s="14">
-        <v>26.923076923076</v>
+        <v>16</v>
       </c>
       <c r="I17" s="15">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="J17" s="15">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K17" s="14">
-        <v>8.536585365853</v>
+        <v>3.296703296703</v>
       </c>
       <c r="L17" s="14">
-        <v>61.818181818181</v>
+        <v>62.068965517241</v>
       </c>
       <c r="M17" s="14">
-        <v>154.285714285714</v>
+        <v>168.571428571429</v>
       </c>
       <c r="N17" s="14">
-        <v>-22.608695652173</v>
+        <v>-27.692307692307</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E18" s="14">
-        <v>-66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="F18" s="15">
+        <v>9</v>
+      </c>
+      <c r="G18" s="15">
         <v>12</v>
       </c>
-      <c r="G18" s="15">
-        <v>14</v>
-      </c>
       <c r="H18" s="14">
-        <v>-14.285714285714</v>
+        <v>-25</v>
       </c>
       <c r="I18" s="15">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J18" s="15">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K18" s="14">
-        <v>-20</v>
+        <v>-19.230769230769</v>
       </c>
       <c r="L18" s="14">
-        <v>-18.367346938775</v>
+        <v>-16</v>
       </c>
       <c r="M18" s="14">
-        <v>-24.528301886792</v>
+        <v>-25</v>
       </c>
       <c r="N18" s="14">
-        <v>-92.844364937388</v>
+        <v>-92.917369308600</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,63 +1057,63 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="D19" s="15">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E19" s="14">
-        <v>0</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="F19" s="15">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="G19" s="15">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H19" s="14">
-        <v>-13.513513513513</v>
+        <v>-20.666666666666</v>
       </c>
       <c r="I19" s="15">
-        <v>440</v>
+        <v>461</v>
       </c>
       <c r="J19" s="15">
-        <v>479</v>
+        <v>515</v>
       </c>
       <c r="K19" s="14">
-        <v>-8.141962421711</v>
+        <v>-10.485436893203</v>
       </c>
       <c r="L19" s="14">
-        <v>-4.555314533622</v>
+        <v>-6.109979633401</v>
       </c>
       <c r="M19" s="14">
-        <v>11.959287531806</v>
+        <v>10.287081339712</v>
       </c>
       <c r="N19" s="14">
-        <v>-75.322490185081</v>
+        <v>-75.825904562139</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="15">
-        <v>1</v>
-      </c>
-      <c r="D20" s="15">
-        <v>2</v>
-      </c>
-      <c r="E20" s="14">
-        <v>-50</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="15">
+        <v>3</v>
+      </c>
+      <c r="G20" s="15">
         <v>5</v>
       </c>
-      <c r="G20" s="15">
-        <v>7</v>
-      </c>
       <c r="H20" s="14">
-        <v>-28.571428571428</v>
+        <v>-40</v>
       </c>
       <c r="I20" s="15">
         <v>9</v>
@@ -1128,10 +1128,10 @@
         <v>-18.181818181818</v>
       </c>
       <c r="M20" s="14">
-        <v>-10</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="N20" s="14">
-        <v>-93.129770992366</v>
+        <v>-93.706293706293</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="D21" s="17">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E21" s="18">
-        <v>10.638297872340</v>
+        <v>-39.215686274509</v>
       </c>
       <c r="F21" s="17">
-        <v>200</v>
+        <v>181</v>
       </c>
       <c r="G21" s="17">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="H21" s="18">
-        <v>-5.660377358490</v>
+        <v>-13.397129186602</v>
       </c>
       <c r="I21" s="17">
-        <v>632</v>
+        <v>664</v>
       </c>
       <c r="J21" s="17">
-        <v>698</v>
+        <v>749</v>
       </c>
       <c r="K21" s="18">
-        <v>-9.455587392550</v>
+        <v>-11.348464619492</v>
       </c>
       <c r="L21" s="18">
-        <v>-0.940438871473</v>
+        <v>-1.337295690936</v>
       </c>
       <c r="M21" s="18">
-        <v>18.352059925093</v>
+        <v>17.314487632508</v>
       </c>
       <c r="N21" s="18">
-        <v>-78.466780238500</v>
+        <v>-78.86023559376</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1183,34 +1183,34 @@
         <v>1</v>
       </c>
       <c r="D22" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22" s="14">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="F22" s="15">
         <v>4</v>
       </c>
       <c r="G22" s="15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H22" s="14">
-        <v>-50</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="I22" s="15">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J22" s="15">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K22" s="14">
-        <v>-22.727272727272</v>
+        <v>-21.739130434782</v>
       </c>
       <c r="L22" s="14">
-        <v>-32</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="M22" s="14">
-        <v>0</v>
+        <v>5.882352941176</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,14 +1220,14 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="15">
-        <v>1</v>
-      </c>
-      <c r="D23" s="15">
-        <v>1</v>
-      </c>
-      <c r="E23" s="14">
-        <v>0</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="15">
         <v>1</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D24" s="15">
+        <v>51</v>
+      </c>
+      <c r="E24" s="14">
+        <v>5.882352941176</v>
+      </c>
+      <c r="F24" s="15">
+        <v>223</v>
+      </c>
+      <c r="G24" s="15">
+        <v>227</v>
+      </c>
+      <c r="H24" s="14">
+        <v>-1.762114537444</v>
+      </c>
+      <c r="I24" s="15">
+        <v>693</v>
+      </c>
+      <c r="J24" s="15">
+        <v>722</v>
+      </c>
+      <c r="K24" s="14">
+        <v>-4.016620498614</v>
+      </c>
+      <c r="L24" s="14">
+        <v>-11.719745222929</v>
+      </c>
+      <c r="M24" s="14">
         <v>50</v>
-      </c>
-      <c r="E24" s="14">
-        <v>-6</v>
-      </c>
-      <c r="F24" s="15">
-        <v>216</v>
-      </c>
-      <c r="G24" s="15">
-        <v>222</v>
-      </c>
-      <c r="H24" s="14">
-        <v>-2.702702702702</v>
-      </c>
-      <c r="I24" s="15">
-        <v>638</v>
-      </c>
-      <c r="J24" s="15">
-        <v>671</v>
-      </c>
-      <c r="K24" s="14">
-        <v>-4.918032786885</v>
-      </c>
-      <c r="L24" s="14">
-        <v>-14.362416107382</v>
-      </c>
-      <c r="M24" s="14">
-        <v>49.414519906323</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D25" s="15">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E25" s="14">
-        <v>7.692307692307</v>
+        <v>0</v>
       </c>
       <c r="F25" s="15">
         <v>195</v>
       </c>
       <c r="G25" s="15">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="H25" s="14">
-        <v>-5.797101449275</v>
+        <v>-4.878048780487</v>
       </c>
       <c r="I25" s="15">
-        <v>595</v>
+        <v>638</v>
       </c>
       <c r="J25" s="15">
-        <v>660</v>
+        <v>703</v>
       </c>
       <c r="K25" s="14">
-        <v>-9.848484848484</v>
+        <v>-9.246088193456</v>
       </c>
       <c r="L25" s="14">
-        <v>-19.811320754717</v>
+        <v>-17.464424320827</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D26" s="15">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E26" s="14">
-        <v>90.909090909090</v>
+        <v>20</v>
       </c>
       <c r="F26" s="15">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="G26" s="15">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H26" s="14">
-        <v>56.363636363636</v>
+        <v>50.943396226415</v>
       </c>
       <c r="I26" s="15">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="J26" s="15">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="K26" s="14">
-        <v>17.159763313609</v>
+        <v>17.318435754189</v>
       </c>
       <c r="L26" s="14">
-        <v>23.75</v>
+        <v>22.093023255814</v>
       </c>
       <c r="M26" s="14">
-        <v>54.6875</v>
+        <v>53.284671532846</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,17 +1387,17 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="15">
-        <v>1</v>
-      </c>
-      <c r="E27" s="14">
-        <v>-100</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G27" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H27" s="14">
         <v>-100</v>
@@ -1428,32 +1428,32 @@
       <c r="C28" s="15">
         <v>1</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="D28" s="15">
+        <v>2</v>
+      </c>
+      <c r="E28" s="14">
+        <v>-50</v>
       </c>
       <c r="F28" s="15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G28" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H28" s="14">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="I28" s="15">
         <v>25</v>
       </c>
       <c r="J28" s="15">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K28" s="14">
-        <v>-24.242424242424</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="L28" s="14">
-        <v>78.571428571428</v>
+        <v>47.058823529411</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1548,35 +1548,35 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="15">
+      <c r="C31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D31" s="15">
         <v>1</v>
       </c>
-      <c r="D31" s="15">
-        <v>4</v>
-      </c>
       <c r="E31" s="14">
-        <v>-75</v>
+        <v>-100</v>
       </c>
       <c r="F31" s="15">
         <v>3</v>
       </c>
       <c r="G31" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H31" s="14">
-        <v>-25</v>
+        <v>-40</v>
       </c>
       <c r="I31" s="15">
         <v>5</v>
       </c>
       <c r="J31" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K31" s="14">
-        <v>-16.666666666666</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="L31" s="14">
-        <v>66.666666666666</v>
+        <v>25</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-018pct.xlsx
+++ b/data/source/weekly/cs-en-us-018pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -892,41 +892,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="15">
+        <v>1</v>
+      </c>
+      <c r="D15" s="15">
+        <v>2</v>
+      </c>
+      <c r="E15" s="14">
+        <v>-50</v>
+      </c>
+      <c r="F15" s="15">
+        <v>1</v>
       </c>
       <c r="G15" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H15" s="14">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I15" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J15" s="15">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K15" s="14">
-        <v>-60</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="L15" s="14">
-        <v>33.333333333333</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M15" s="14">
-        <v>-50</v>
+        <v>-37.5</v>
       </c>
       <c r="N15" s="14">
-        <v>-66.666666666666</v>
+        <v>-58.333333333333</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D16" s="15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E16" s="14">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F16" s="15">
         <v>21</v>
       </c>
       <c r="G16" s="15">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="H16" s="14">
-        <v>40</v>
+        <v>133.333333333333</v>
       </c>
       <c r="I16" s="15">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="J16" s="15">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K16" s="14">
-        <v>-14.285714285714</v>
+        <v>-7.8125</v>
       </c>
       <c r="L16" s="14">
-        <v>-8.474576271186</v>
+        <v>-3.278688524590</v>
       </c>
       <c r="M16" s="14">
-        <v>54.285714285714</v>
+        <v>63.888888888888</v>
       </c>
       <c r="N16" s="14">
-        <v>-84.615384615384</v>
+        <v>-84.224598930481</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D17" s="15">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E17" s="14">
-        <v>-55.555555555555</v>
+        <v>80</v>
       </c>
       <c r="F17" s="15">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G17" s="15">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H17" s="14">
-        <v>16</v>
+        <v>18.518518518518</v>
       </c>
       <c r="I17" s="15">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="J17" s="15">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="K17" s="14">
-        <v>3.296703296703</v>
+        <v>5.208333333333</v>
       </c>
       <c r="L17" s="14">
-        <v>62.068965517241</v>
+        <v>42.253521126760</v>
       </c>
       <c r="M17" s="14">
-        <v>168.571428571429</v>
+        <v>172.972972972973</v>
       </c>
       <c r="N17" s="14">
-        <v>-27.692307692307</v>
+        <v>-29.861111111111</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D18" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E18" s="14">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F18" s="15">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G18" s="15">
         <v>12</v>
       </c>
       <c r="H18" s="14">
-        <v>-25</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="I18" s="15">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="J18" s="15">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="K18" s="14">
-        <v>-19.230769230769</v>
+        <v>-16.071428571428</v>
       </c>
       <c r="L18" s="14">
-        <v>-16</v>
+        <v>-16.071428571428</v>
       </c>
       <c r="M18" s="14">
-        <v>-25</v>
+        <v>-18.965517241379</v>
       </c>
       <c r="N18" s="14">
-        <v>-92.917369308600</v>
+        <v>-92.679127725856</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D19" s="15">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="E19" s="14">
-        <v>-41.666666666666</v>
+        <v>3.571428571428</v>
       </c>
       <c r="F19" s="15">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="G19" s="15">
-        <v>150</v>
+        <v>131</v>
       </c>
       <c r="H19" s="14">
-        <v>-20.666666666666</v>
+        <v>-13.740458015267</v>
       </c>
       <c r="I19" s="15">
-        <v>461</v>
+        <v>489</v>
       </c>
       <c r="J19" s="15">
-        <v>515</v>
+        <v>543</v>
       </c>
       <c r="K19" s="14">
-        <v>-10.485436893203</v>
+        <v>-9.944751381215</v>
       </c>
       <c r="L19" s="14">
-        <v>-6.109979633401</v>
+        <v>-8.082706766917</v>
       </c>
       <c r="M19" s="14">
-        <v>10.287081339712</v>
+        <v>7.947019867549</v>
       </c>
       <c r="N19" s="14">
-        <v>-75.825904562139</v>
+        <v>-76.192794547224</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1100,38 +1100,38 @@
       <c r="C20" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="D20" s="15">
+        <v>1</v>
+      </c>
+      <c r="E20" s="14">
+        <v>-100</v>
       </c>
       <c r="F20" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G20" s="15">
         <v>5</v>
       </c>
       <c r="H20" s="14">
-        <v>-40</v>
+        <v>-60</v>
       </c>
       <c r="I20" s="15">
         <v>9</v>
       </c>
       <c r="J20" s="15">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K20" s="14">
-        <v>-50</v>
+        <v>-52.631578947368</v>
       </c>
       <c r="L20" s="14">
-        <v>-18.181818181818</v>
+        <v>-25</v>
       </c>
       <c r="M20" s="14">
         <v>-18.181818181818</v>
       </c>
       <c r="N20" s="14">
-        <v>-93.706293706293</v>
+        <v>-94.039735099337</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="D21" s="17">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="E21" s="18">
-        <v>-39.215686274509</v>
+        <v>19.512195121951</v>
       </c>
       <c r="F21" s="17">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G21" s="17">
-        <v>209</v>
+        <v>187</v>
       </c>
       <c r="H21" s="18">
-        <v>-13.397129186602</v>
+        <v>-3.743315508021</v>
       </c>
       <c r="I21" s="17">
-        <v>664</v>
+        <v>710</v>
       </c>
       <c r="J21" s="17">
-        <v>749</v>
+        <v>790</v>
       </c>
       <c r="K21" s="18">
-        <v>-11.348464619492</v>
+        <v>-10.126582278481</v>
       </c>
       <c r="L21" s="18">
-        <v>-1.337295690936</v>
+        <v>-3.532608695652</v>
       </c>
       <c r="M21" s="18">
-        <v>17.314487632508</v>
+        <v>17.161716171617</v>
       </c>
       <c r="N21" s="18">
-        <v>-78.86023559376</v>
+        <v>-79.006505026611</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1189,28 +1189,28 @@
         <v>0</v>
       </c>
       <c r="F22" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G22" s="15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H22" s="14">
-        <v>-42.857142857142</v>
+        <v>0</v>
       </c>
       <c r="I22" s="15">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J22" s="15">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K22" s="14">
-        <v>-21.739130434782</v>
+        <v>-20.833333333333</v>
       </c>
       <c r="L22" s="14">
-        <v>-30.769230769230</v>
+        <v>-32.142857142857</v>
       </c>
       <c r="M22" s="14">
-        <v>5.882352941176</v>
+        <v>5.555555555555</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="D24" s="15">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E24" s="14">
-        <v>5.882352941176</v>
+        <v>-4.081632653061</v>
       </c>
       <c r="F24" s="15">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="G24" s="15">
-        <v>227</v>
+        <v>208</v>
       </c>
       <c r="H24" s="14">
-        <v>-1.762114537444</v>
+        <v>4.807692307692</v>
       </c>
       <c r="I24" s="15">
-        <v>693</v>
+        <v>740</v>
       </c>
       <c r="J24" s="15">
-        <v>722</v>
+        <v>771</v>
       </c>
       <c r="K24" s="14">
-        <v>-4.016620498614</v>
+        <v>-4.020752269779</v>
       </c>
       <c r="L24" s="14">
-        <v>-11.719745222929</v>
+        <v>-11.270983213429</v>
       </c>
       <c r="M24" s="14">
-        <v>50</v>
+        <v>45.669291338582</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D25" s="15">
         <v>43</v>
       </c>
       <c r="E25" s="14">
-        <v>0</v>
+        <v>-2.325581395348</v>
       </c>
       <c r="F25" s="15">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="G25" s="15">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H25" s="14">
-        <v>-4.878048780487</v>
+        <v>-3.208556149732</v>
       </c>
       <c r="I25" s="15">
-        <v>638</v>
+        <v>680</v>
       </c>
       <c r="J25" s="15">
-        <v>703</v>
+        <v>746</v>
       </c>
       <c r="K25" s="14">
-        <v>-9.246088193456</v>
+        <v>-8.847184986595</v>
       </c>
       <c r="L25" s="14">
-        <v>-17.464424320827</v>
+        <v>-18.269230769230</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
+        <v>20</v>
+      </c>
+      <c r="D26" s="15">
         <v>12</v>
       </c>
-      <c r="D26" s="15">
-        <v>10</v>
-      </c>
       <c r="E26" s="14">
-        <v>20</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F26" s="15">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G26" s="15">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H26" s="14">
-        <v>50.943396226415</v>
+        <v>55.769230769230</v>
       </c>
       <c r="I26" s="15">
-        <v>210</v>
+        <v>231</v>
       </c>
       <c r="J26" s="15">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="K26" s="14">
-        <v>17.318435754189</v>
+        <v>20.942408376963</v>
       </c>
       <c r="L26" s="14">
-        <v>22.093023255814</v>
+        <v>24.193548387096</v>
       </c>
       <c r="M26" s="14">
-        <v>53.284671532846</v>
+        <v>60.416666666666</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="15">
+        <v>1</v>
+      </c>
+      <c r="D27" s="15">
+        <v>2</v>
+      </c>
+      <c r="E27" s="14">
+        <v>-50</v>
+      </c>
+      <c r="F27" s="15">
+        <v>1</v>
       </c>
       <c r="G27" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H27" s="14">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I27" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J27" s="15">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K27" s="14">
-        <v>-63.636363636363</v>
+        <v>-61.538461538461</v>
       </c>
       <c r="L27" s="14">
-        <v>-20</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D28" s="15">
         <v>2</v>
       </c>
       <c r="E28" s="14">
-        <v>-50</v>
+        <v>100</v>
       </c>
       <c r="F28" s="15">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G28" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H28" s="14">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="I28" s="15">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J28" s="15">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K28" s="14">
-        <v>-28.571428571428</v>
+        <v>-21.621621621621</v>
       </c>
       <c r="L28" s="14">
-        <v>47.058823529411</v>
+        <v>38.095238095238</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1551,20 +1551,20 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="15">
-        <v>1</v>
-      </c>
-      <c r="E31" s="14">
-        <v>-100</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G31" s="15">
         <v>5</v>
       </c>
       <c r="H31" s="14">
-        <v>-40</v>
+        <v>-60</v>
       </c>
       <c r="I31" s="15">
         <v>5</v>

--- a/data/source/weekly/cs-en-us-018pct.xlsx
+++ b/data/source/weekly/cs-en-us-018pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -329,8 +329,8 @@
   <numFmts count="5">
     <numFmt numFmtId="164" formatCode="#0"/>
     <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0;&quot;-&quot;#,##0.0"/>
-    <numFmt numFmtId="167" formatCode="#,##0"/>
+    <numFmt numFmtId="166" formatCode="#,##0"/>
+    <numFmt numFmtId="167" formatCode="#,##0.0;&quot;-&quot;#,##0.0"/>
     <numFmt numFmtId="168" formatCode="#,##0.00;&quot;-&quot;#,##0.00"/>
   </numFmts>
   <fonts count="12">
@@ -546,7 +546,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -564,7 +564,7 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>20</v>
+      <c r="C14" s="14">
+        <v>1</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -860,8 +860,8 @@
       <c r="E14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="13" t="s">
-        <v>20</v>
+      <c r="F14" s="14">
+        <v>1</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>20</v>
@@ -869,8 +869,8 @@
       <c r="H14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I14" s="13" t="s">
-        <v>20</v>
+      <c r="I14" s="14">
+        <v>1</v>
       </c>
       <c r="J14" s="13" t="s">
         <v>20</v>
@@ -878,54 +878,54 @@
       <c r="K14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L14" s="14">
-        <v>-100</v>
-      </c>
-      <c r="M14" s="14">
-        <v>-100</v>
-      </c>
-      <c r="N14" s="14">
-        <v>-100</v>
+      <c r="L14" s="15">
+        <v>0</v>
+      </c>
+      <c r="M14" s="15">
+        <v>-66.666666666666</v>
+      </c>
+      <c r="N14" s="15">
+        <v>-83.333333333333</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="14">
         <v>1</v>
       </c>
-      <c r="D15" s="15">
-        <v>2</v>
-      </c>
-      <c r="E15" s="14">
-        <v>-50</v>
-      </c>
-      <c r="F15" s="15">
+      <c r="E15" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F15" s="14">
         <v>1</v>
       </c>
-      <c r="G15" s="15">
-        <v>3</v>
-      </c>
-      <c r="H15" s="14">
-        <v>-66.666666666666</v>
-      </c>
-      <c r="I15" s="15">
+      <c r="G15" s="14">
+        <v>4</v>
+      </c>
+      <c r="H15" s="15">
+        <v>-75</v>
+      </c>
+      <c r="I15" s="14">
         <v>5</v>
       </c>
-      <c r="J15" s="15">
-        <v>12</v>
-      </c>
-      <c r="K15" s="14">
-        <v>-58.333333333333</v>
-      </c>
-      <c r="L15" s="14">
+      <c r="J15" s="14">
+        <v>13</v>
+      </c>
+      <c r="K15" s="15">
+        <v>-61.538461538461</v>
+      </c>
+      <c r="L15" s="15">
         <v>66.666666666666</v>
       </c>
-      <c r="M15" s="14">
+      <c r="M15" s="15">
         <v>-37.5</v>
       </c>
-      <c r="N15" s="14">
+      <c r="N15" s="15">
         <v>-58.333333333333</v>
       </c>
     </row>
@@ -933,205 +933,205 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="15">
-        <v>5</v>
-      </c>
-      <c r="D16" s="15">
-        <v>1</v>
-      </c>
-      <c r="E16" s="14">
-        <v>400</v>
-      </c>
-      <c r="F16" s="15">
-        <v>21</v>
-      </c>
-      <c r="G16" s="15">
-        <v>9</v>
-      </c>
-      <c r="H16" s="14">
-        <v>133.333333333333</v>
-      </c>
-      <c r="I16" s="15">
-        <v>59</v>
-      </c>
-      <c r="J16" s="15">
-        <v>64</v>
-      </c>
-      <c r="K16" s="14">
-        <v>-7.8125</v>
-      </c>
-      <c r="L16" s="14">
-        <v>-3.278688524590</v>
-      </c>
-      <c r="M16" s="14">
-        <v>63.888888888888</v>
-      </c>
-      <c r="N16" s="14">
-        <v>-84.224598930481</v>
+      <c r="C16" s="14">
+        <v>3</v>
+      </c>
+      <c r="D16" s="14">
+        <v>7</v>
+      </c>
+      <c r="E16" s="15">
+        <v>-57.142857142857</v>
+      </c>
+      <c r="F16" s="14">
+        <v>21</v>
+      </c>
+      <c r="G16" s="14">
+        <v>13</v>
+      </c>
+      <c r="H16" s="15">
+        <v>61.538461538461</v>
+      </c>
+      <c r="I16" s="14">
+        <v>62</v>
+      </c>
+      <c r="J16" s="14">
+        <v>71</v>
+      </c>
+      <c r="K16" s="15">
+        <v>-12.676056338028</v>
+      </c>
+      <c r="L16" s="15">
+        <v>0</v>
+      </c>
+      <c r="M16" s="15">
+        <v>63.157894736842</v>
+      </c>
+      <c r="N16" s="15">
+        <v>-84.691358024691</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="15">
-        <v>9</v>
-      </c>
-      <c r="D17" s="15">
+      <c r="C17" s="14">
         <v>5</v>
       </c>
-      <c r="E17" s="14">
-        <v>80</v>
-      </c>
-      <c r="F17" s="15">
-        <v>32</v>
-      </c>
-      <c r="G17" s="15">
-        <v>27</v>
-      </c>
-      <c r="H17" s="14">
-        <v>18.518518518518</v>
-      </c>
-      <c r="I17" s="15">
-        <v>101</v>
-      </c>
-      <c r="J17" s="15">
-        <v>96</v>
-      </c>
-      <c r="K17" s="14">
-        <v>5.208333333333</v>
-      </c>
-      <c r="L17" s="14">
-        <v>42.253521126760</v>
-      </c>
-      <c r="M17" s="14">
-        <v>172.972972972973</v>
-      </c>
-      <c r="N17" s="14">
-        <v>-29.861111111111</v>
+      <c r="D17" s="14">
+        <v>7</v>
+      </c>
+      <c r="E17" s="15">
+        <v>-28.571428571428</v>
+      </c>
+      <c r="F17" s="14">
+        <v>25</v>
+      </c>
+      <c r="G17" s="14">
+        <v>28</v>
+      </c>
+      <c r="H17" s="15">
+        <v>-10.714285714285</v>
+      </c>
+      <c r="I17" s="14">
+        <v>106</v>
+      </c>
+      <c r="J17" s="14">
+        <v>103</v>
+      </c>
+      <c r="K17" s="15">
+        <v>2.912621359223</v>
+      </c>
+      <c r="L17" s="15">
+        <v>32.5</v>
+      </c>
+      <c r="M17" s="15">
+        <v>165</v>
+      </c>
+      <c r="N17" s="15">
+        <v>-32.484076433121</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="15">
-        <v>5</v>
-      </c>
-      <c r="D18" s="15">
+      <c r="C18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="14">
         <v>4</v>
       </c>
-      <c r="E18" s="14">
-        <v>25</v>
-      </c>
-      <c r="F18" s="15">
-        <v>11</v>
-      </c>
-      <c r="G18" s="15">
-        <v>12</v>
-      </c>
-      <c r="H18" s="14">
-        <v>-8.333333333333</v>
-      </c>
-      <c r="I18" s="15">
+      <c r="E18" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F18" s="14">
+        <v>8</v>
+      </c>
+      <c r="G18" s="14">
+        <v>13</v>
+      </c>
+      <c r="H18" s="15">
+        <v>-38.461538461538</v>
+      </c>
+      <c r="I18" s="14">
         <v>47</v>
       </c>
-      <c r="J18" s="15">
-        <v>56</v>
-      </c>
-      <c r="K18" s="14">
-        <v>-16.071428571428</v>
-      </c>
-      <c r="L18" s="14">
-        <v>-16.071428571428</v>
-      </c>
-      <c r="M18" s="14">
-        <v>-18.965517241379</v>
-      </c>
-      <c r="N18" s="14">
-        <v>-92.679127725856</v>
+      <c r="J18" s="14">
+        <v>60</v>
+      </c>
+      <c r="K18" s="15">
+        <v>-21.666666666666</v>
+      </c>
+      <c r="L18" s="15">
+        <v>-22.950819672131</v>
+      </c>
+      <c r="M18" s="15">
+        <v>-21.666666666666</v>
+      </c>
+      <c r="N18" s="15">
+        <v>-93.178519593613</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="15">
-        <v>29</v>
-      </c>
-      <c r="D19" s="15">
-        <v>28</v>
-      </c>
-      <c r="E19" s="14">
-        <v>3.571428571428</v>
-      </c>
-      <c r="F19" s="15">
-        <v>113</v>
-      </c>
-      <c r="G19" s="15">
-        <v>131</v>
-      </c>
-      <c r="H19" s="14">
-        <v>-13.740458015267</v>
-      </c>
-      <c r="I19" s="15">
-        <v>489</v>
-      </c>
-      <c r="J19" s="15">
-        <v>543</v>
-      </c>
-      <c r="K19" s="14">
-        <v>-9.944751381215</v>
-      </c>
-      <c r="L19" s="14">
-        <v>-8.082706766917</v>
-      </c>
-      <c r="M19" s="14">
-        <v>7.947019867549</v>
-      </c>
-      <c r="N19" s="14">
-        <v>-76.192794547224</v>
+      <c r="C19" s="14">
+        <v>30</v>
+      </c>
+      <c r="D19" s="14">
+        <v>26</v>
+      </c>
+      <c r="E19" s="15">
+        <v>15.384615384615</v>
+      </c>
+      <c r="F19" s="14">
+        <v>111</v>
+      </c>
+      <c r="G19" s="14">
+        <v>123</v>
+      </c>
+      <c r="H19" s="15">
+        <v>-9.756097560975</v>
+      </c>
+      <c r="I19" s="14">
+        <v>518</v>
+      </c>
+      <c r="J19" s="14">
+        <v>569</v>
+      </c>
+      <c r="K19" s="15">
+        <v>-8.963093145869</v>
+      </c>
+      <c r="L19" s="15">
+        <v>-8.156028368794</v>
+      </c>
+      <c r="M19" s="15">
+        <v>6.584362139917</v>
+      </c>
+      <c r="N19" s="15">
+        <v>-76.454545454545</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="15">
-        <v>1</v>
-      </c>
-      <c r="E20" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F20" s="15">
+      <c r="C20" s="14">
         <v>2</v>
       </c>
-      <c r="G20" s="15">
-        <v>5</v>
-      </c>
-      <c r="H20" s="14">
-        <v>-60</v>
-      </c>
-      <c r="I20" s="15">
-        <v>9</v>
-      </c>
-      <c r="J20" s="15">
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F20" s="14">
+        <v>3</v>
+      </c>
+      <c r="G20" s="14">
+        <v>3</v>
+      </c>
+      <c r="H20" s="15">
+        <v>0</v>
+      </c>
+      <c r="I20" s="14">
+        <v>11</v>
+      </c>
+      <c r="J20" s="14">
         <v>19</v>
       </c>
-      <c r="K20" s="14">
-        <v>-52.631578947368</v>
-      </c>
-      <c r="L20" s="14">
-        <v>-25</v>
-      </c>
-      <c r="M20" s="14">
-        <v>-18.181818181818</v>
-      </c>
-      <c r="N20" s="14">
-        <v>-94.039735099337</v>
+      <c r="K20" s="15">
+        <v>-42.105263157894</v>
+      </c>
+      <c r="L20" s="15">
+        <v>-8.333333333333</v>
+      </c>
+      <c r="M20" s="15">
+        <v>-15.384615384615</v>
+      </c>
+      <c r="N20" s="15">
+        <v>-93.333333333333</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="D21" s="17">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E21" s="18">
-        <v>19.512195121951</v>
+        <v>-8.888888888888</v>
       </c>
       <c r="F21" s="17">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="G21" s="17">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H21" s="18">
-        <v>-3.743315508021</v>
+        <v>-7.608695652173</v>
       </c>
       <c r="I21" s="17">
-        <v>710</v>
+        <v>750</v>
       </c>
       <c r="J21" s="17">
-        <v>790</v>
+        <v>835</v>
       </c>
       <c r="K21" s="18">
-        <v>-10.126582278481</v>
+        <v>-10.179640718562</v>
       </c>
       <c r="L21" s="18">
-        <v>-3.532608695652</v>
+        <v>-4.214559386973</v>
       </c>
       <c r="M21" s="18">
-        <v>17.161716171617</v>
+        <v>15.740740740740</v>
       </c>
       <c r="N21" s="18">
-        <v>-79.006505026611</v>
+        <v>-79.361585030269</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="15">
+      <c r="C22" s="14">
+        <v>2</v>
+      </c>
+      <c r="D22" s="14">
         <v>1</v>
       </c>
-      <c r="D22" s="15">
-        <v>1</v>
-      </c>
-      <c r="E22" s="14">
+      <c r="E22" s="15">
+        <v>100</v>
+      </c>
+      <c r="F22" s="14">
+        <v>5</v>
+      </c>
+      <c r="G22" s="14">
+        <v>5</v>
+      </c>
+      <c r="H22" s="15">
         <v>0</v>
       </c>
-      <c r="F22" s="15">
+      <c r="I22" s="14">
+        <v>21</v>
+      </c>
+      <c r="J22" s="14">
+        <v>25</v>
+      </c>
+      <c r="K22" s="15">
+        <v>-16</v>
+      </c>
+      <c r="L22" s="15">
+        <v>-25</v>
+      </c>
+      <c r="M22" s="15">
         <v>5</v>
-      </c>
-      <c r="G22" s="15">
-        <v>5</v>
-      </c>
-      <c r="H22" s="14">
-        <v>0</v>
-      </c>
-      <c r="I22" s="15">
-        <v>19</v>
-      </c>
-      <c r="J22" s="15">
-        <v>24</v>
-      </c>
-      <c r="K22" s="14">
-        <v>-20.833333333333</v>
-      </c>
-      <c r="L22" s="14">
-        <v>-32.142857142857</v>
-      </c>
-      <c r="M22" s="14">
-        <v>5.555555555555</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1229,25 +1229,25 @@
       <c r="E23" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F23" s="15">
+      <c r="F23" s="14">
         <v>1</v>
       </c>
-      <c r="G23" s="15">
+      <c r="G23" s="14">
         <v>1</v>
       </c>
-      <c r="H23" s="14">
+      <c r="H23" s="15">
         <v>0</v>
       </c>
-      <c r="I23" s="15">
+      <c r="I23" s="14">
         <v>1</v>
       </c>
-      <c r="J23" s="15">
+      <c r="J23" s="14">
         <v>2</v>
       </c>
-      <c r="K23" s="14">
+      <c r="K23" s="15">
         <v>-50</v>
       </c>
-      <c r="L23" s="14">
+      <c r="L23" s="15">
         <v>0</v>
       </c>
       <c r="M23" s="13" t="s">
@@ -1261,38 +1261,38 @@
       <c r="A24" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C24" s="15">
+      <c r="C24" s="14">
+        <v>44</v>
+      </c>
+      <c r="D24" s="14">
         <v>47</v>
       </c>
-      <c r="D24" s="15">
-        <v>49</v>
-      </c>
-      <c r="E24" s="14">
-        <v>-4.081632653061</v>
-      </c>
-      <c r="F24" s="15">
-        <v>218</v>
-      </c>
-      <c r="G24" s="15">
-        <v>208</v>
-      </c>
-      <c r="H24" s="14">
-        <v>4.807692307692</v>
-      </c>
-      <c r="I24" s="15">
-        <v>740</v>
-      </c>
-      <c r="J24" s="15">
-        <v>771</v>
-      </c>
-      <c r="K24" s="14">
-        <v>-4.020752269779</v>
-      </c>
-      <c r="L24" s="14">
-        <v>-11.270983213429</v>
-      </c>
-      <c r="M24" s="14">
-        <v>45.669291338582</v>
+      <c r="E24" s="15">
+        <v>-6.382978723404</v>
+      </c>
+      <c r="F24" s="14">
+        <v>196</v>
+      </c>
+      <c r="G24" s="14">
+        <v>197</v>
+      </c>
+      <c r="H24" s="15">
+        <v>-0.507614213197</v>
+      </c>
+      <c r="I24" s="14">
+        <v>787</v>
+      </c>
+      <c r="J24" s="14">
+        <v>818</v>
+      </c>
+      <c r="K24" s="15">
+        <v>-3.789731051344</v>
+      </c>
+      <c r="L24" s="15">
+        <v>-9.954233409610</v>
+      </c>
+      <c r="M24" s="15">
+        <v>46.554934823091</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1302,35 +1302,35 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="15">
-        <v>42</v>
-      </c>
-      <c r="D25" s="15">
-        <v>43</v>
-      </c>
-      <c r="E25" s="14">
-        <v>-2.325581395348</v>
-      </c>
-      <c r="F25" s="15">
-        <v>181</v>
-      </c>
-      <c r="G25" s="15">
-        <v>187</v>
-      </c>
-      <c r="H25" s="14">
-        <v>-3.208556149732</v>
-      </c>
-      <c r="I25" s="15">
-        <v>680</v>
-      </c>
-      <c r="J25" s="15">
-        <v>746</v>
-      </c>
-      <c r="K25" s="14">
-        <v>-8.847184986595</v>
-      </c>
-      <c r="L25" s="14">
-        <v>-18.269230769230</v>
+      <c r="C25" s="14">
+        <v>41</v>
+      </c>
+      <c r="D25" s="14">
+        <v>40</v>
+      </c>
+      <c r="E25" s="15">
+        <v>2.5</v>
+      </c>
+      <c r="F25" s="14">
+        <v>170</v>
+      </c>
+      <c r="G25" s="14">
+        <v>165</v>
+      </c>
+      <c r="H25" s="15">
+        <v>3.030303030303</v>
+      </c>
+      <c r="I25" s="14">
+        <v>723</v>
+      </c>
+      <c r="J25" s="14">
+        <v>786</v>
+      </c>
+      <c r="K25" s="15">
+        <v>-8.015267175572</v>
+      </c>
+      <c r="L25" s="15">
+        <v>-17.182130584192</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1343,38 +1343,38 @@
       <c r="A26" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C26" s="15">
-        <v>20</v>
-      </c>
-      <c r="D26" s="15">
-        <v>12</v>
-      </c>
-      <c r="E26" s="14">
-        <v>66.666666666666</v>
-      </c>
-      <c r="F26" s="15">
-        <v>81</v>
-      </c>
-      <c r="G26" s="15">
-        <v>52</v>
-      </c>
-      <c r="H26" s="14">
-        <v>55.769230769230</v>
-      </c>
-      <c r="I26" s="15">
-        <v>231</v>
-      </c>
-      <c r="J26" s="15">
-        <v>191</v>
-      </c>
-      <c r="K26" s="14">
-        <v>20.942408376963</v>
-      </c>
-      <c r="L26" s="14">
-        <v>24.193548387096</v>
-      </c>
-      <c r="M26" s="14">
-        <v>60.416666666666</v>
+      <c r="C26" s="14">
+        <v>26</v>
+      </c>
+      <c r="D26" s="14">
+        <v>17</v>
+      </c>
+      <c r="E26" s="15">
+        <v>52.941176470588</v>
+      </c>
+      <c r="F26" s="14">
+        <v>80</v>
+      </c>
+      <c r="G26" s="14">
+        <v>50</v>
+      </c>
+      <c r="H26" s="15">
+        <v>60</v>
+      </c>
+      <c r="I26" s="14">
+        <v>257</v>
+      </c>
+      <c r="J26" s="14">
+        <v>208</v>
+      </c>
+      <c r="K26" s="15">
+        <v>23.557692307692</v>
+      </c>
+      <c r="L26" s="15">
+        <v>25.980392156862</v>
+      </c>
+      <c r="M26" s="15">
+        <v>63.694267515923</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,34 +1384,34 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="15">
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="15">
-        <v>2</v>
-      </c>
-      <c r="E27" s="14">
-        <v>-50</v>
-      </c>
-      <c r="F27" s="15">
+      <c r="E27" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F27" s="14">
         <v>1</v>
       </c>
-      <c r="G27" s="15">
-        <v>3</v>
-      </c>
-      <c r="H27" s="14">
-        <v>-66.666666666666</v>
-      </c>
-      <c r="I27" s="15">
+      <c r="G27" s="14">
+        <v>4</v>
+      </c>
+      <c r="H27" s="15">
+        <v>-75</v>
+      </c>
+      <c r="I27" s="14">
         <v>5</v>
       </c>
-      <c r="J27" s="15">
-        <v>13</v>
-      </c>
-      <c r="K27" s="14">
-        <v>-61.538461538461</v>
-      </c>
-      <c r="L27" s="14">
+      <c r="J27" s="14">
+        <v>14</v>
+      </c>
+      <c r="K27" s="15">
+        <v>-64.285714285714</v>
+      </c>
+      <c r="L27" s="15">
         <v>-16.666666666666</v>
       </c>
       <c r="M27" s="13" t="s">
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
-        <v>4</v>
-      </c>
-      <c r="D28" s="15">
-        <v>2</v>
-      </c>
-      <c r="E28" s="14">
-        <v>100</v>
-      </c>
-      <c r="F28" s="15">
-        <v>8</v>
-      </c>
-      <c r="G28" s="15">
-        <v>4</v>
-      </c>
-      <c r="H28" s="14">
-        <v>100</v>
-      </c>
-      <c r="I28" s="15">
-        <v>29</v>
-      </c>
-      <c r="J28" s="15">
-        <v>37</v>
-      </c>
-      <c r="K28" s="14">
-        <v>-21.621621621621</v>
-      </c>
-      <c r="L28" s="14">
-        <v>38.095238095238</v>
+      <c r="C28" s="14">
+        <v>1</v>
+      </c>
+      <c r="D28" s="14">
+        <v>5</v>
+      </c>
+      <c r="E28" s="15">
+        <v>-80</v>
+      </c>
+      <c r="F28" s="14">
+        <v>7</v>
+      </c>
+      <c r="G28" s="14">
+        <v>9</v>
+      </c>
+      <c r="H28" s="15">
+        <v>-22.222222222222</v>
+      </c>
+      <c r="I28" s="14">
+        <v>30</v>
+      </c>
+      <c r="J28" s="14">
+        <v>42</v>
+      </c>
+      <c r="K28" s="15">
+        <v>-28.571428571428</v>
+      </c>
+      <c r="L28" s="15">
+        <v>20</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1493,13 +1493,13 @@
       <c r="K29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L29" s="14">
+      <c r="L29" s="15">
         <v>-100</v>
       </c>
-      <c r="M29" s="14">
+      <c r="M29" s="15">
         <v>-100</v>
       </c>
-      <c r="N29" s="14">
+      <c r="N29" s="15">
         <v>-100</v>
       </c>
     </row>
@@ -1534,13 +1534,13 @@
       <c r="K30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L30" s="14">
+      <c r="L30" s="15">
         <v>-100</v>
       </c>
-      <c r="M30" s="14">
+      <c r="M30" s="15">
         <v>-100</v>
       </c>
-      <c r="N30" s="14">
+      <c r="N30" s="15">
         <v>-100</v>
       </c>
     </row>
@@ -1557,25 +1557,25 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="15">
-        <v>2</v>
-      </c>
-      <c r="G31" s="15">
+      <c r="F31" s="14">
+        <v>1</v>
+      </c>
+      <c r="G31" s="14">
         <v>5</v>
       </c>
-      <c r="H31" s="14">
-        <v>-60</v>
-      </c>
-      <c r="I31" s="15">
+      <c r="H31" s="15">
+        <v>-80</v>
+      </c>
+      <c r="I31" s="14">
         <v>5</v>
       </c>
-      <c r="J31" s="15">
+      <c r="J31" s="14">
         <v>7</v>
       </c>
-      <c r="K31" s="14">
+      <c r="K31" s="15">
         <v>-28.571428571428</v>
       </c>
-      <c r="L31" s="14">
+      <c r="L31" s="15">
         <v>25</v>
       </c>
       <c r="M31" s="13" t="s">
@@ -1628,10 +1628,10 @@
       <c r="I33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="J33" s="15">
+      <c r="J33" s="14">
         <v>3</v>
       </c>
-      <c r="K33" s="14">
+      <c r="K33" s="15">
         <v>-100</v>
       </c>
       <c r="L33" s="13" t="s">
@@ -1742,31 +1742,31 @@
       <c r="A39" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C39" s="15">
+      <c r="C39" s="14">
         <v>16</v>
       </c>
-      <c r="E39" s="15">
+      <c r="E39" s="14">
         <v>11</v>
       </c>
-      <c r="G39" s="15">
+      <c r="G39" s="14">
         <v>3</v>
       </c>
-      <c r="I39" s="15">
+      <c r="I39" s="14">
         <v>5</v>
       </c>
-      <c r="J39" s="15">
+      <c r="J39" s="14">
         <v>7</v>
       </c>
-      <c r="K39" s="14">
+      <c r="K39" s="15">
         <v>40</v>
       </c>
-      <c r="L39" s="14">
+      <c r="L39" s="15">
         <v>133.333333333333</v>
       </c>
-      <c r="M39" s="14">
+      <c r="M39" s="15">
         <v>-36.363636363636</v>
       </c>
-      <c r="N39" s="14">
+      <c r="N39" s="15">
         <v>-56.25</v>
       </c>
     </row>
@@ -1774,31 +1774,31 @@
       <c r="A40" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C40" s="15">
+      <c r="C40" s="14">
         <v>18</v>
       </c>
-      <c r="E40" s="15">
+      <c r="E40" s="14">
         <v>26</v>
       </c>
-      <c r="G40" s="15">
+      <c r="G40" s="14">
         <v>22</v>
       </c>
-      <c r="I40" s="15">
+      <c r="I40" s="14">
         <v>17</v>
       </c>
-      <c r="J40" s="15">
+      <c r="J40" s="14">
         <v>32</v>
       </c>
-      <c r="K40" s="14">
+      <c r="K40" s="15">
         <v>88.235294117647</v>
       </c>
-      <c r="L40" s="14">
+      <c r="L40" s="15">
         <v>45.454545454545</v>
       </c>
-      <c r="M40" s="14">
+      <c r="M40" s="15">
         <v>23.076923076923</v>
       </c>
-      <c r="N40" s="14">
+      <c r="N40" s="15">
         <v>77.777777777777</v>
       </c>
     </row>
@@ -1806,31 +1806,31 @@
       <c r="A41" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C41" s="15">
+      <c r="C41" s="14">
         <v>2135</v>
       </c>
-      <c r="E41" s="15">
+      <c r="E41" s="14">
         <v>1388</v>
       </c>
-      <c r="G41" s="15">
+      <c r="G41" s="14">
         <v>595</v>
       </c>
-      <c r="I41" s="15">
+      <c r="I41" s="14">
         <v>394</v>
       </c>
-      <c r="J41" s="15">
+      <c r="J41" s="14">
         <v>249</v>
       </c>
-      <c r="K41" s="14">
+      <c r="K41" s="15">
         <v>-36.802030456852</v>
       </c>
-      <c r="L41" s="14">
+      <c r="L41" s="15">
         <v>-58.151260504201</v>
       </c>
-      <c r="M41" s="14">
+      <c r="M41" s="15">
         <v>-82.060518731988</v>
       </c>
-      <c r="N41" s="14">
+      <c r="N41" s="15">
         <v>-88.337236533957</v>
       </c>
     </row>
@@ -1838,31 +1838,31 @@
       <c r="A42" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C42" s="15">
+      <c r="C42" s="14">
         <v>389</v>
       </c>
-      <c r="E42" s="15">
+      <c r="E42" s="14">
         <v>496</v>
       </c>
-      <c r="G42" s="15">
+      <c r="G42" s="14">
         <v>343</v>
       </c>
-      <c r="I42" s="15">
+      <c r="I42" s="14">
         <v>251</v>
       </c>
-      <c r="J42" s="15">
+      <c r="J42" s="14">
         <v>336</v>
       </c>
-      <c r="K42" s="14">
+      <c r="K42" s="15">
         <v>33.864541832669</v>
       </c>
-      <c r="L42" s="14">
+      <c r="L42" s="15">
         <v>-2.040816326530</v>
       </c>
-      <c r="M42" s="14">
+      <c r="M42" s="15">
         <v>-32.258064516129</v>
       </c>
-      <c r="N42" s="14">
+      <c r="N42" s="15">
         <v>-13.624678663239</v>
       </c>
     </row>
@@ -1870,31 +1870,31 @@
       <c r="A43" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C43" s="15">
+      <c r="C43" s="14">
         <v>2912</v>
       </c>
-      <c r="E43" s="15">
+      <c r="E43" s="14">
         <v>2161</v>
       </c>
-      <c r="G43" s="15">
+      <c r="G43" s="14">
         <v>993</v>
       </c>
-      <c r="I43" s="15">
+      <c r="I43" s="14">
         <v>462</v>
       </c>
-      <c r="J43" s="15">
+      <c r="J43" s="14">
         <v>192</v>
       </c>
-      <c r="K43" s="14">
+      <c r="K43" s="15">
         <v>-58.441558441558</v>
       </c>
-      <c r="L43" s="14">
+      <c r="L43" s="15">
         <v>-80.664652567975</v>
       </c>
-      <c r="M43" s="14">
+      <c r="M43" s="15">
         <v>-91.115224433132</v>
       </c>
-      <c r="N43" s="14">
+      <c r="N43" s="15">
         <v>-93.406593406593</v>
       </c>
     </row>
@@ -1902,31 +1902,31 @@
       <c r="A44" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C44" s="15">
+      <c r="C44" s="14">
         <v>8903</v>
       </c>
-      <c r="E44" s="15">
+      <c r="E44" s="14">
         <v>7683</v>
       </c>
-      <c r="G44" s="15">
+      <c r="G44" s="14">
         <v>4242</v>
       </c>
-      <c r="I44" s="15">
+      <c r="I44" s="14">
         <v>3966</v>
       </c>
-      <c r="J44" s="15">
+      <c r="J44" s="14">
         <v>1778</v>
       </c>
-      <c r="K44" s="14">
+      <c r="K44" s="15">
         <v>-55.168935955622</v>
       </c>
-      <c r="L44" s="14">
+      <c r="L44" s="15">
         <v>-58.085808580858</v>
       </c>
-      <c r="M44" s="14">
+      <c r="M44" s="15">
         <v>-76.857998177795</v>
       </c>
-      <c r="N44" s="14">
+      <c r="N44" s="15">
         <v>-80.029203639222</v>
       </c>
     </row>
@@ -1934,31 +1934,31 @@
       <c r="A45" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C45" s="15">
+      <c r="C45" s="14">
         <v>1012</v>
       </c>
-      <c r="E45" s="15">
+      <c r="E45" s="14">
         <v>511</v>
       </c>
-      <c r="G45" s="15">
+      <c r="G45" s="14">
         <v>331</v>
       </c>
-      <c r="I45" s="15">
+      <c r="I45" s="14">
         <v>201</v>
       </c>
-      <c r="J45" s="15">
+      <c r="J45" s="14">
         <v>53</v>
       </c>
-      <c r="K45" s="14">
+      <c r="K45" s="15">
         <v>-73.631840796019</v>
       </c>
-      <c r="L45" s="14">
+      <c r="L45" s="15">
         <v>-83.987915407855</v>
       </c>
-      <c r="M45" s="14">
+      <c r="M45" s="15">
         <v>-89.628180039138</v>
       </c>
-      <c r="N45" s="14">
+      <c r="N45" s="15">
         <v>-94.762845849802</v>
       </c>
     </row>

--- a/data/source/weekly/cs-en-us-018pct.xlsx
+++ b/data/source/weekly/cs-en-us-018pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="14">
-        <v>1</v>
+      <c r="C14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -885,48 +885,48 @@
         <v>-66.666666666666</v>
       </c>
       <c r="N14" s="15">
-        <v>-83.333333333333</v>
+        <v>-85.714285714285</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>1</v>
       </c>
       <c r="D15" s="14">
         <v>1</v>
       </c>
       <c r="E15" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="14">
         <v>4</v>
       </c>
       <c r="H15" s="15">
-        <v>-75</v>
+        <v>-50</v>
       </c>
       <c r="I15" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J15" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K15" s="15">
-        <v>-61.538461538461</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="L15" s="15">
-        <v>66.666666666666</v>
+        <v>100</v>
       </c>
       <c r="M15" s="15">
-        <v>-37.5</v>
+        <v>-25</v>
       </c>
       <c r="N15" s="15">
-        <v>-58.333333333333</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D16" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E16" s="15">
-        <v>-57.142857142857</v>
+        <v>-25</v>
       </c>
       <c r="F16" s="14">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G16" s="14">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H16" s="15">
-        <v>61.538461538461</v>
+        <v>-10</v>
       </c>
       <c r="I16" s="14">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="J16" s="14">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K16" s="15">
-        <v>-12.676056338028</v>
+        <v>-13.924050632911</v>
       </c>
       <c r="L16" s="15">
-        <v>0</v>
+        <v>4.615384615384</v>
       </c>
       <c r="M16" s="15">
-        <v>63.157894736842</v>
+        <v>70</v>
       </c>
       <c r="N16" s="15">
-        <v>-84.691358024691</v>
+        <v>-84.259259259259</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D17" s="14">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E17" s="15">
-        <v>-28.571428571428</v>
+        <v>-53.846153846153</v>
       </c>
       <c r="F17" s="14">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G17" s="14">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H17" s="15">
-        <v>-10.714285714285</v>
+        <v>-35.294117647058</v>
       </c>
       <c r="I17" s="14">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="J17" s="14">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="K17" s="15">
-        <v>2.912621359223</v>
+        <v>-4.310344827586</v>
       </c>
       <c r="L17" s="15">
-        <v>32.5</v>
+        <v>29.069767441860</v>
       </c>
       <c r="M17" s="15">
-        <v>165</v>
+        <v>152.272727272727</v>
       </c>
       <c r="N17" s="15">
-        <v>-32.484076433121</v>
+        <v>-34.319526627218</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="14">
+        <v>3</v>
       </c>
       <c r="D18" s="14">
         <v>4</v>
       </c>
       <c r="E18" s="15">
-        <v>-100</v>
+        <v>-25</v>
       </c>
       <c r="F18" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G18" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H18" s="15">
-        <v>-38.461538461538</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="I18" s="14">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="J18" s="14">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="K18" s="15">
-        <v>-21.666666666666</v>
+        <v>-21.875</v>
       </c>
       <c r="L18" s="15">
-        <v>-22.950819672131</v>
+        <v>-21.875</v>
       </c>
       <c r="M18" s="15">
-        <v>-21.666666666666</v>
+        <v>-21.875</v>
       </c>
       <c r="N18" s="15">
-        <v>-93.178519593613</v>
+        <v>-93.112947658402</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D19" s="14">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="E19" s="15">
-        <v>15.384615384615</v>
+        <v>-26.315789473684</v>
       </c>
       <c r="F19" s="14">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="G19" s="14">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="H19" s="15">
-        <v>-9.756097560975</v>
+        <v>-16.40625</v>
       </c>
       <c r="I19" s="14">
-        <v>518</v>
+        <v>547</v>
       </c>
       <c r="J19" s="14">
-        <v>569</v>
+        <v>607</v>
       </c>
       <c r="K19" s="15">
-        <v>-8.963093145869</v>
+        <v>-9.884678747940</v>
       </c>
       <c r="L19" s="15">
-        <v>-8.156028368794</v>
+        <v>-7.130730050933</v>
       </c>
       <c r="M19" s="15">
-        <v>6.584362139917</v>
+        <v>6.627680311890</v>
       </c>
       <c r="N19" s="15">
-        <v>-76.454545454545</v>
+        <v>-76.733304976605</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
+      <c r="C20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="14">
+        <v>3</v>
+      </c>
+      <c r="E20" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F20" s="14">
         <v>2</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F20" s="14">
-        <v>3</v>
-      </c>
       <c r="G20" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H20" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I20" s="14">
         <v>11</v>
       </c>
       <c r="J20" s="14">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K20" s="15">
-        <v>-42.105263157894</v>
+        <v>-50</v>
       </c>
       <c r="L20" s="15">
-        <v>-8.333333333333</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="M20" s="15">
         <v>-15.384615384615</v>
       </c>
       <c r="N20" s="15">
-        <v>-93.333333333333</v>
+        <v>-93.75</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D21" s="17">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="E21" s="18">
-        <v>-8.888888888888</v>
+        <v>-34.328358208955</v>
       </c>
       <c r="F21" s="17">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="G21" s="17">
-        <v>184</v>
+        <v>204</v>
       </c>
       <c r="H21" s="18">
-        <v>-7.608695652173</v>
+        <v>-20.588235294117</v>
       </c>
       <c r="I21" s="17">
-        <v>750</v>
+        <v>794</v>
       </c>
       <c r="J21" s="17">
-        <v>835</v>
+        <v>902</v>
       </c>
       <c r="K21" s="18">
-        <v>-10.179640718562</v>
+        <v>-11.973392461197</v>
       </c>
       <c r="L21" s="18">
-        <v>-4.214559386973</v>
+        <v>-3.406326034063</v>
       </c>
       <c r="M21" s="18">
-        <v>15.740740740740</v>
+        <v>15.912408759124</v>
       </c>
       <c r="N21" s="18">
-        <v>-79.361585030269</v>
+        <v>-79.499096307771</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1183,34 +1183,34 @@
         <v>2</v>
       </c>
       <c r="D22" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E22" s="15">
-        <v>100</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F22" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G22" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H22" s="15">
         <v>0</v>
       </c>
       <c r="I22" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J22" s="14">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K22" s="15">
-        <v>-16</v>
+        <v>-17.857142857142</v>
       </c>
       <c r="L22" s="15">
-        <v>-25</v>
+        <v>-23.333333333333</v>
       </c>
       <c r="M22" s="15">
-        <v>5</v>
+        <v>9.523809523809</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1229,14 +1229,14 @@
       <c r="E23" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F23" s="14">
-        <v>1</v>
-      </c>
-      <c r="G23" s="14">
-        <v>1</v>
-      </c>
-      <c r="H23" s="15">
-        <v>0</v>
+      <c r="F23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I23" s="14">
         <v>1</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="D24" s="14">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E24" s="15">
-        <v>-6.382978723404</v>
+        <v>20</v>
       </c>
       <c r="F24" s="14">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="G24" s="14">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="H24" s="15">
-        <v>-0.507614213197</v>
+        <v>4.166666666666</v>
       </c>
       <c r="I24" s="14">
-        <v>787</v>
+        <v>840</v>
       </c>
       <c r="J24" s="14">
-        <v>818</v>
+        <v>863</v>
       </c>
       <c r="K24" s="15">
-        <v>-3.789731051344</v>
+        <v>-2.665121668597</v>
       </c>
       <c r="L24" s="15">
-        <v>-9.954233409610</v>
+        <v>-8.695652173913</v>
       </c>
       <c r="M24" s="15">
-        <v>46.554934823091</v>
+        <v>47.887323943662</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
+        <v>36</v>
+      </c>
+      <c r="D25" s="14">
         <v>41</v>
       </c>
-      <c r="D25" s="14">
-        <v>40</v>
-      </c>
       <c r="E25" s="15">
-        <v>2.5</v>
+        <v>-12.195121951219</v>
       </c>
       <c r="F25" s="14">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="G25" s="14">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H25" s="15">
-        <v>3.030303030303</v>
+        <v>-1.796407185628</v>
       </c>
       <c r="I25" s="14">
-        <v>723</v>
+        <v>759</v>
       </c>
       <c r="J25" s="14">
-        <v>786</v>
+        <v>827</v>
       </c>
       <c r="K25" s="15">
-        <v>-8.015267175572</v>
+        <v>-8.222490931076</v>
       </c>
       <c r="L25" s="15">
-        <v>-17.182130584192</v>
+        <v>-17.768147345612</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="D26" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E26" s="15">
-        <v>52.941176470588</v>
+        <v>-5.555555555555</v>
       </c>
       <c r="F26" s="14">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="G26" s="14">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="H26" s="15">
-        <v>60</v>
+        <v>35.087719298245</v>
       </c>
       <c r="I26" s="14">
-        <v>257</v>
+        <v>275</v>
       </c>
       <c r="J26" s="14">
-        <v>208</v>
+        <v>226</v>
       </c>
       <c r="K26" s="15">
-        <v>23.557692307692</v>
+        <v>21.681415929203</v>
       </c>
       <c r="L26" s="15">
-        <v>25.980392156862</v>
+        <v>26.146788990825</v>
       </c>
       <c r="M26" s="15">
-        <v>63.694267515923</v>
+        <v>66.666666666666</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>1</v>
       </c>
       <c r="D27" s="14">
         <v>1</v>
       </c>
       <c r="E27" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27" s="14">
         <v>4</v>
       </c>
       <c r="H27" s="15">
-        <v>-75</v>
+        <v>-50</v>
       </c>
       <c r="I27" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J27" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K27" s="15">
-        <v>-64.285714285714</v>
+        <v>-60</v>
       </c>
       <c r="L27" s="15">
-        <v>-16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D28" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E28" s="15">
-        <v>-80</v>
+        <v>50</v>
       </c>
       <c r="F28" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G28" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H28" s="15">
-        <v>-22.222222222222</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="I28" s="14">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J28" s="14">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K28" s="15">
-        <v>-28.571428571428</v>
+        <v>-25</v>
       </c>
       <c r="L28" s="15">
-        <v>20</v>
+        <v>26.923076923076</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,29 +1469,29 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="D29" s="14">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15">
+        <v>-100</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>21</v>
+      <c r="G29" s="14">
+        <v>1</v>
+      </c>
+      <c r="H29" s="15">
+        <v>-100</v>
       </c>
       <c r="I29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="J29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K29" s="13" t="s">
-        <v>21</v>
+      <c r="J29" s="14">
+        <v>1</v>
+      </c>
+      <c r="K29" s="15">
+        <v>-100</v>
       </c>
       <c r="L29" s="15">
         <v>-100</v>
@@ -1510,29 +1510,29 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>-100</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H30" s="13" t="s">
-        <v>21</v>
+      <c r="G30" s="14">
+        <v>1</v>
+      </c>
+      <c r="H30" s="15">
+        <v>-100</v>
       </c>
       <c r="I30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="J30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K30" s="13" t="s">
-        <v>21</v>
+      <c r="J30" s="14">
+        <v>1</v>
+      </c>
+      <c r="K30" s="15">
+        <v>-100</v>
       </c>
       <c r="L30" s="15">
         <v>-100</v>
@@ -1551,29 +1551,29 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F31" s="14">
+      <c r="D31" s="14">
         <v>1</v>
       </c>
+      <c r="E31" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F31" s="13" t="s">
+        <v>20</v>
+      </c>
       <c r="G31" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H31" s="15">
-        <v>-80</v>
+        <v>-100</v>
       </c>
       <c r="I31" s="14">
         <v>5</v>
       </c>
       <c r="J31" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K31" s="15">
-        <v>-28.571428571428</v>
+        <v>-37.5</v>
       </c>
       <c r="L31" s="15">
         <v>25</v>

--- a/data/source/weekly/cs-en-us-018pct.xlsx
+++ b/data/source/weekly/cs-en-us-018pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -885,7 +885,7 @@
         <v>-66.666666666666</v>
       </c>
       <c r="N14" s="15">
-        <v>-85.714285714285</v>
+        <v>-87.5</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -893,40 +893,40 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>1</v>
-      </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G15" s="14">
         <v>4</v>
       </c>
       <c r="H15" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I15" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J15" s="14">
         <v>14</v>
       </c>
       <c r="K15" s="15">
-        <v>-57.142857142857</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="L15" s="15">
-        <v>100</v>
+        <v>166.666666666667</v>
       </c>
       <c r="M15" s="15">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="N15" s="15">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D16" s="14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E16" s="15">
-        <v>-25</v>
+        <v>25</v>
       </c>
       <c r="F16" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G16" s="14">
         <v>20</v>
       </c>
       <c r="H16" s="15">
-        <v>-10</v>
+        <v>-5</v>
       </c>
       <c r="I16" s="14">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="J16" s="14">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="K16" s="15">
-        <v>-13.924050632911</v>
+        <v>-12.048192771084</v>
       </c>
       <c r="L16" s="15">
-        <v>4.615384615384</v>
+        <v>5.797101449275</v>
       </c>
       <c r="M16" s="15">
-        <v>70</v>
+        <v>73.809523809523</v>
       </c>
       <c r="N16" s="15">
-        <v>-84.259259259259</v>
+        <v>-84.164859002169</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D17" s="14">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E17" s="15">
-        <v>-53.846153846153</v>
+        <v>28.571428571428</v>
       </c>
       <c r="F17" s="14">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G17" s="14">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H17" s="15">
-        <v>-35.294117647058</v>
+        <v>-15.625</v>
       </c>
       <c r="I17" s="14">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="J17" s="14">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="K17" s="15">
-        <v>-4.310344827586</v>
+        <v>-3.252032520325</v>
       </c>
       <c r="L17" s="15">
-        <v>29.069767441860</v>
+        <v>29.347826086956</v>
       </c>
       <c r="M17" s="15">
-        <v>152.272727272727</v>
+        <v>138</v>
       </c>
       <c r="N17" s="15">
-        <v>-34.319526627218</v>
+        <v>-32.768361581920</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D18" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E18" s="15">
-        <v>-25</v>
+        <v>12.5</v>
       </c>
       <c r="F18" s="14">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G18" s="14">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H18" s="15">
-        <v>-28.571428571428</v>
+        <v>-15</v>
       </c>
       <c r="I18" s="14">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="J18" s="14">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="K18" s="15">
-        <v>-21.875</v>
+        <v>-18.055555555555</v>
       </c>
       <c r="L18" s="15">
-        <v>-21.875</v>
+        <v>-13.235294117647</v>
       </c>
       <c r="M18" s="15">
-        <v>-21.875</v>
+        <v>-15.714285714285</v>
       </c>
       <c r="N18" s="15">
-        <v>-93.112947658402</v>
+        <v>-92.257217847769</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D19" s="14">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="E19" s="15">
-        <v>-26.315789473684</v>
+        <v>6.666666666666</v>
       </c>
       <c r="F19" s="14">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="G19" s="14">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="H19" s="15">
-        <v>-16.40625</v>
+        <v>-3.278688524590</v>
       </c>
       <c r="I19" s="14">
-        <v>547</v>
+        <v>579</v>
       </c>
       <c r="J19" s="14">
-        <v>607</v>
+        <v>637</v>
       </c>
       <c r="K19" s="15">
-        <v>-9.884678747940</v>
+        <v>-9.105180533751</v>
       </c>
       <c r="L19" s="15">
-        <v>-7.130730050933</v>
+        <v>-7.949125596184</v>
       </c>
       <c r="M19" s="15">
-        <v>6.627680311890</v>
+        <v>5.272727272727</v>
       </c>
       <c r="N19" s="15">
-        <v>-76.733304976605</v>
+        <v>-76.558704453441</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,7 +1101,7 @@
         <v>20</v>
       </c>
       <c r="D20" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E20" s="15">
         <v>-100</v>
@@ -1110,28 +1110,28 @@
         <v>2</v>
       </c>
       <c r="G20" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H20" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I20" s="14">
         <v>11</v>
       </c>
       <c r="J20" s="14">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K20" s="15">
-        <v>-50</v>
+        <v>-54.166666666666</v>
       </c>
       <c r="L20" s="15">
+        <v>-26.666666666666</v>
+      </c>
+      <c r="M20" s="15">
         <v>-21.428571428571</v>
       </c>
-      <c r="M20" s="15">
-        <v>-15.384615384615</v>
-      </c>
       <c r="N20" s="15">
-        <v>-93.75</v>
+        <v>-93.922651933701</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="D21" s="17">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="E21" s="18">
-        <v>-34.328358208955</v>
+        <v>11.764705882352</v>
       </c>
       <c r="F21" s="17">
-        <v>162</v>
+        <v>188</v>
       </c>
       <c r="G21" s="17">
         <v>204</v>
       </c>
       <c r="H21" s="18">
-        <v>-20.588235294117</v>
+        <v>-7.843137254901</v>
       </c>
       <c r="I21" s="17">
-        <v>794</v>
+        <v>850</v>
       </c>
       <c r="J21" s="17">
-        <v>902</v>
+        <v>953</v>
       </c>
       <c r="K21" s="18">
-        <v>-11.973392461197</v>
+        <v>-10.807974816369</v>
       </c>
       <c r="L21" s="18">
-        <v>-3.406326034063</v>
+        <v>-3.078677309007</v>
       </c>
       <c r="M21" s="18">
-        <v>15.912408759124</v>
+        <v>15.332428765264</v>
       </c>
       <c r="N21" s="18">
-        <v>-79.499096307771</v>
+        <v>-79.120609186932</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,19 +1180,19 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>2</v>
-      </c>
-      <c r="D22" s="14">
-        <v>3</v>
-      </c>
-      <c r="E22" s="15">
-        <v>-33.333333333333</v>
+        <v>1</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G22" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H22" s="15">
         <v>0</v>
@@ -1207,7 +1207,7 @@
         <v>-17.857142857142</v>
       </c>
       <c r="L22" s="15">
-        <v>-23.333333333333</v>
+        <v>-34.285714285714</v>
       </c>
       <c r="M22" s="15">
         <v>9.523809523809</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="D24" s="14">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E24" s="15">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F24" s="14">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="G24" s="14">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="H24" s="15">
-        <v>4.166666666666</v>
+        <v>2.717391304347</v>
       </c>
       <c r="I24" s="14">
-        <v>840</v>
+        <v>883</v>
       </c>
       <c r="J24" s="14">
-        <v>863</v>
+        <v>906</v>
       </c>
       <c r="K24" s="15">
-        <v>-2.665121668597</v>
+        <v>-2.538631346578</v>
       </c>
       <c r="L24" s="15">
-        <v>-8.695652173913</v>
+        <v>-10.081466395112</v>
       </c>
       <c r="M24" s="15">
-        <v>47.887323943662</v>
+        <v>45.469522240527</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D25" s="14">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E25" s="15">
-        <v>-12.195121951219</v>
+        <v>5.128205128205</v>
       </c>
       <c r="F25" s="14">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="G25" s="14">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="H25" s="15">
-        <v>-1.796407185628</v>
+        <v>-0.613496932515</v>
       </c>
       <c r="I25" s="14">
-        <v>759</v>
+        <v>800</v>
       </c>
       <c r="J25" s="14">
-        <v>827</v>
+        <v>866</v>
       </c>
       <c r="K25" s="15">
-        <v>-8.222490931076</v>
+        <v>-7.621247113163</v>
       </c>
       <c r="L25" s="15">
-        <v>-17.768147345612</v>
+        <v>-19.028340080971</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D26" s="14">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E26" s="15">
-        <v>-5.555555555555</v>
+        <v>0</v>
       </c>
       <c r="F26" s="14">
         <v>77</v>
       </c>
       <c r="G26" s="14">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="H26" s="15">
-        <v>35.087719298245</v>
+        <v>28.333333333333</v>
       </c>
       <c r="I26" s="14">
-        <v>275</v>
+        <v>289</v>
       </c>
       <c r="J26" s="14">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="K26" s="15">
-        <v>21.681415929203</v>
+        <v>20.920502092050</v>
       </c>
       <c r="L26" s="15">
-        <v>26.146788990825</v>
+        <v>26.200873362445</v>
       </c>
       <c r="M26" s="15">
-        <v>66.666666666666</v>
+        <v>67.052023121387</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>1</v>
-      </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G27" s="14">
         <v>4</v>
       </c>
       <c r="H27" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I27" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J27" s="14">
         <v>15</v>
       </c>
       <c r="K27" s="15">
-        <v>-60</v>
+        <v>-46.666666666666</v>
       </c>
       <c r="L27" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D28" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F28" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G28" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H28" s="15">
-        <v>-18.181818181818</v>
+        <v>0</v>
       </c>
       <c r="I28" s="14">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J28" s="14">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K28" s="15">
-        <v>-25</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="L28" s="15">
-        <v>26.923076923076</v>
+        <v>16.666666666666</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,11 +1469,11 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="14">
-        <v>1</v>
-      </c>
-      <c r="E29" s="15">
-        <v>-100</v>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
@@ -1510,11 +1510,11 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="14">
-        <v>1</v>
-      </c>
-      <c r="E30" s="15">
-        <v>-100</v>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
@@ -1548,35 +1548,35 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D31" s="14">
+      <c r="C31" s="14">
         <v>1</v>
       </c>
-      <c r="E31" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F31" s="14">
+        <v>1</v>
       </c>
       <c r="G31" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H31" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I31" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J31" s="14">
         <v>8</v>
       </c>
       <c r="K31" s="15">
-        <v>-37.5</v>
+        <v>-25</v>
       </c>
       <c r="L31" s="15">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
